--- a/Dowling/dowling-vs-dcg-091126.xlsx
+++ b/Dowling/dowling-vs-dcg-091126.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1abc75c8e08b2b2b/Desktop/GitHub/Dowling-Football/Dowling/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_A5D3E148B84A547458831BBC888216B2618541A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE478FC-3DA1-4C7B-81F9-8948BE13823A}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rbcc2a8912a4546b8"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="87">
   <si>
     <t>PLAY #</t>
   </si>
@@ -276,11 +285,870 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y151"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -357,7 +1225,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -386,7 +1254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -442,7 +1310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -498,7 +1366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -551,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -607,7 +1475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -666,7 +1534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -722,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -778,7 +1646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -834,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -884,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -943,7 +1811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -999,7 +1867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1055,7 +1923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1108,7 +1976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1161,7 +2029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1199,7 +2067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1255,7 +2123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1287,7 +2155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1343,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1396,7 +2264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1452,7 +2320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1505,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1558,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1608,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1640,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1693,7 +2561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1737,7 +2605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1790,7 +2658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1843,7 +2711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1875,7 +2743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1928,7 +2796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1978,7 +2846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2025,7 +2893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2075,7 +2943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2125,7 +2993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2175,7 +3043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2225,7 +3093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2257,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2286,7 +3154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2342,7 +3210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2395,7 +3263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2451,7 +3319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2507,7 +3375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2566,7 +3434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2598,7 +3466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2642,7 +3510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2692,7 +3560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2748,7 +3616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2801,7 +3669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2833,7 +3701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2886,7 +3754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2939,7 +3807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2995,7 +3863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3030,7 +3898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3080,7 +3948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3130,7 +3998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3183,7 +4051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3236,7 +4104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3286,7 +4154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3336,7 +4204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3389,7 +4257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3442,7 +4310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3492,7 +4360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3542,7 +4410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3574,7 +4442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3606,7 +4474,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3662,7 +4530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3715,7 +4583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3765,7 +4633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3818,7 +4686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3868,7 +4736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3900,7 +4768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3953,7 +4821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4003,7 +4871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4038,7 +4906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4088,7 +4956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4138,7 +5006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4182,7 +5050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4229,7 +5097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4282,7 +5150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4314,7 +5182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4370,7 +5238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4423,7 +5291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4479,7 +5347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4532,7 +5400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4585,7 +5453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4641,7 +5509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4691,7 +5559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4747,7 +5615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4779,7 +5647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4811,7 +5679,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4843,7 +5711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4893,7 +5761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4946,7 +5814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4996,7 +5864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5046,7 +5914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5096,7 +5964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5146,7 +6014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5196,7 +6064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5246,7 +6114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5296,7 +6164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5328,7 +6196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5360,7 +6228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5389,7 +6257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5430,7 +6298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5483,7 +6351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5539,7 +6407,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5586,7 +6454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5618,7 +6486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5668,7 +6536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5718,7 +6586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5768,7 +6636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5818,7 +6686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5868,7 +6736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5900,7 +6768,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5932,7 +6800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5985,7 +6853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6041,7 +6909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6094,7 +6962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6144,7 +7012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6194,7 +7062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6244,7 +7112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6297,7 +7165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6347,7 +7215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6379,7 +7247,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6408,7 +7276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6461,7 +7329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6514,7 +7382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6567,7 +7435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6599,7 +7467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6631,7 +7499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6681,7 +7549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6725,7 +7593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6775,7 +7643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6825,7 +7693,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -6875,7 +7743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6925,7 +7793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6975,7 +7843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7025,7 +7893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7075,7 +7943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7125,7 +7993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7157,7 +8025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7189,7 +8057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7245,7 +8113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7298,7 +8166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7351,7 +8219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7383,7 +8251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7436,7 +8304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7486,7 +8354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7537,5 +8405,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dowling/dowling-vs-dcg-091126.xlsx
+++ b/Dowling/dowling-vs-dcg-091126.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1abc75c8e08b2b2b/Desktop/GitHub/Dowling-Football/Dowling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_A5D3E148B84A547458831BBC888216B2618541A1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE478FC-3DA1-4C7B-81F9-8948BE13823A}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Rc079442b0d4e464e"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0">
   <si>
     <t>PLAY #</t>
   </si>
@@ -124,6 +115,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>TWINS WING</t>
   </si>
   <si>
@@ -148,6 +142,9 @@
     <t>EMPTY</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Incomplete</t>
   </si>
   <si>
@@ -235,6 +232,9 @@
     <t>TWINS PRO</t>
   </si>
   <si>
+    <t>E-Alley</t>
+  </si>
+  <si>
     <t>DOUBLE WING</t>
   </si>
   <si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>OMAHA</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>Complete, TD</t>
@@ -285,870 +288,11 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:Y151"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.36328125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1254,7 +398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1291,17 +435,20 @@
       <c r="L3">
         <v>7</v>
       </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
       <c r="R3" t="s">
         <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U3" t="s">
         <v>30</v>
       </c>
       <c r="V3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -1310,7 +457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1333,16 +480,16 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -1350,14 +497,17 @@
       <c r="N4">
         <v>9</v>
       </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
       <c r="R4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -1366,7 +516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1386,7 +536,7 @@
         <v>-30</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
         <v>31</v>
@@ -1398,19 +548,22 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5">
         <v>7</v>
       </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
       <c r="R5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1419,7 +572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1439,7 +592,7 @@
         <v>-34</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>31</v>
@@ -1456,12 +609,15 @@
       <c r="L6">
         <v>7</v>
       </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
       <c r="R6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" t="s">
         <v>35</v>
       </c>
-      <c r="S6" t="s">
-        <v>34</v>
-      </c>
       <c r="U6" t="s">
         <v>30</v>
       </c>
@@ -1475,7 +631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1498,16 +654,16 @@
         <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1515,14 +671,17 @@
       <c r="N7">
         <v>0</v>
       </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V7" t="s">
         <v>30</v>
@@ -1534,7 +693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1557,16 +716,16 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -1574,14 +733,17 @@
       <c r="N8">
         <v>8</v>
       </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
       <c r="R8" t="s">
         <v>30</v>
       </c>
       <c r="S8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W8">
         <v>3</v>
@@ -1590,7 +752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1610,13 +772,13 @@
         <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -1630,14 +792,17 @@
       <c r="N9">
         <v>2</v>
       </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
       <c r="R9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W9">
         <v>3</v>
@@ -1646,7 +811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1666,19 +831,19 @@
         <v>-41</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -1686,11 +851,14 @@
       <c r="N10">
         <v>0</v>
       </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
       <c r="R10" t="s">
         <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U10" t="s">
         <v>30</v>
@@ -1702,7 +870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1734,16 +902,19 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
+      <c r="M11" t="s">
+        <v>43</v>
+      </c>
       <c r="R11" t="s">
         <v>30</v>
       </c>
       <c r="U11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W11">
         <v>3</v>
@@ -1752,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1775,10 +946,10 @@
         <v>26</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1792,17 +963,20 @@
       <c r="N12">
         <v>25</v>
       </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
       <c r="R12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W12">
         <v>3</v>
@@ -1811,7 +985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1834,10 +1008,10 @@
         <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1851,11 +1025,14 @@
       <c r="N13">
         <v>10</v>
       </c>
+      <c r="O13">
+        <v>6</v>
+      </c>
       <c r="R13" t="s">
         <v>30</v>
       </c>
       <c r="S13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U13" t="s">
         <v>30</v>
@@ -1867,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1890,16 +1067,16 @@
         <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J14">
         <v>12</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1907,23 +1084,26 @@
       <c r="N14">
         <v>12</v>
       </c>
+      <c r="O14">
+        <v>4</v>
+      </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
       <c r="S14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1943,7 +1123,7 @@
         <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
         <v>31</v>
@@ -1960,14 +1140,17 @@
       <c r="L15">
         <v>7</v>
       </c>
+      <c r="M15" t="s">
+        <v>34</v>
+      </c>
       <c r="R15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W15">
         <v>3</v>
@@ -1976,7 +1159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1996,7 +1179,7 @@
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
         <v>31</v>
@@ -2013,14 +1196,17 @@
       <c r="L16">
         <v>7</v>
       </c>
+      <c r="M16" t="s">
+        <v>29</v>
+      </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
       <c r="S16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2029,7 +1215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2049,10 +1235,10 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J17">
         <v>-5</v>
@@ -2067,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2087,13 +1273,13 @@
         <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2107,23 +1293,26 @@
       <c r="N18">
         <v>32</v>
       </c>
+      <c r="O18">
+        <v>8</v>
+      </c>
       <c r="R18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U18" t="s">
         <v>30</v>
       </c>
       <c r="W18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2143,19 +1332,19 @@
         <v>37</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2163,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2187,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -2196,10 +1385,10 @@
         <v>30</v>
       </c>
       <c r="S20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U20" t="s">
         <v>30</v>
@@ -2211,7 +1400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2219,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2249,13 +1438,13 @@
         <v>7</v>
       </c>
       <c r="R21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U21" t="s">
         <v>30</v>
@@ -2264,7 +1453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2272,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -2287,10 +1476,10 @@
         <v>26</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -2304,23 +1493,26 @@
       <c r="N22">
         <v>4</v>
       </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
       <c r="R22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2328,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2340,19 +1532,19 @@
         <v>-23</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -2360,11 +1552,14 @@
       <c r="N23">
         <v>8</v>
       </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
       <c r="R23" t="s">
         <v>30</v>
       </c>
       <c r="S23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U23" t="s">
         <v>30</v>
@@ -2373,7 +1568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2381,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2393,19 +1588,19 @@
         <v>-23</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2413,11 +1608,14 @@
       <c r="N24">
         <v>9</v>
       </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
       <c r="R24" t="s">
         <v>30</v>
       </c>
       <c r="S24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U24" t="s">
         <v>30</v>
@@ -2426,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2434,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -2446,19 +1644,19 @@
         <v>-23</v>
       </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J25">
         <v>-10</v>
       </c>
       <c r="K25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2467,7 +1665,7 @@
         <v>30</v>
       </c>
       <c r="S25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U25" t="s">
         <v>30</v>
@@ -2476,7 +1674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2499,16 +1697,16 @@
         <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2528,7 +1726,7 @@
         <v>-33</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H27" t="s">
         <v>31</v>
@@ -2545,14 +1743,17 @@
       <c r="L27">
         <v>7</v>
       </c>
+      <c r="M27" t="s">
+        <v>43</v>
+      </c>
       <c r="R27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W27">
         <v>3</v>
@@ -2561,7 +1762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2581,13 +1782,13 @@
         <v>-32</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
         <v>31</v>
       </c>
       <c r="I28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J28">
         <v>-5</v>
@@ -2599,13 +1800,13 @@
         <v>30</v>
       </c>
       <c r="S28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="X28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2625,7 +1826,7 @@
         <v>-27</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H29" t="s">
         <v>31</v>
@@ -2642,14 +1843,17 @@
       <c r="L29">
         <v>7</v>
       </c>
+      <c r="M29" t="s">
+        <v>43</v>
+      </c>
       <c r="R29" t="s">
         <v>30</v>
       </c>
       <c r="S29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W29">
         <v>3</v>
@@ -2658,7 +1862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2678,13 +1882,13 @@
         <v>-29</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2698,8 +1902,11 @@
       <c r="N30">
         <v>4</v>
       </c>
+      <c r="O30">
+        <v>3</v>
+      </c>
       <c r="R30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U30" t="s">
         <v>30</v>
@@ -2711,7 +1918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2731,19 +1938,19 @@
         <v>-29</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2751,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2766,10 +1973,10 @@
         <v>26</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -2783,20 +1990,23 @@
       <c r="N32">
         <v>5</v>
       </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
       <c r="R32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2804,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2834,19 +2044,19 @@
         <v>8</v>
       </c>
       <c r="R33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2854,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2866,7 +2076,7 @@
         <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H34" t="s">
         <v>31</v>
@@ -2893,7 +2103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2901,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2913,13 +2123,13 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -2933,17 +2143,20 @@
       <c r="N35">
         <v>5</v>
       </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
       <c r="R35" t="s">
         <v>30</v>
       </c>
       <c r="U35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2951,7 +2164,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2963,7 +2176,7 @@
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H36" t="s">
         <v>31</v>
@@ -2975,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -2984,7 +2197,7 @@
         <v>30</v>
       </c>
       <c r="S36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U36" t="s">
         <v>30</v>
@@ -2993,7 +2206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3001,7 +2214,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -3013,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I37" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J37">
         <v>12</v>
@@ -3031,10 +2244,10 @@
         <v>7</v>
       </c>
       <c r="R37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U37" t="s">
         <v>30</v>
@@ -3043,7 +2256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3051,7 +2264,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -3069,7 +2282,7 @@
         <v>31</v>
       </c>
       <c r="I38" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J38">
         <v>3</v>
@@ -3081,10 +2294,10 @@
         <v>9</v>
       </c>
       <c r="R38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U38" t="s">
         <v>30</v>
@@ -3093,7 +2306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3116,16 +2329,16 @@
         <v>26</v>
       </c>
       <c r="H39" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I39" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3154,7 +2367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3177,16 +2390,16 @@
         <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J41">
         <v>8</v>
       </c>
       <c r="K41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L41">
         <v>7</v>
@@ -3194,14 +2407,17 @@
       <c r="N41">
         <v>8</v>
       </c>
+      <c r="O41">
+        <v>2</v>
+      </c>
       <c r="R41" t="s">
+        <v>36</v>
+      </c>
+      <c r="S41" t="s">
         <v>35</v>
       </c>
-      <c r="S41" t="s">
-        <v>34</v>
-      </c>
       <c r="U41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W41">
         <v>3</v>
@@ -3210,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3230,7 +2446,7 @@
         <v>-28</v>
       </c>
       <c r="G42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H42" t="s">
         <v>31</v>
@@ -3242,16 +2458,19 @@
         <v>4</v>
       </c>
       <c r="K42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
+      <c r="M42" t="s">
+        <v>29</v>
+      </c>
       <c r="R42" t="s">
         <v>30</v>
       </c>
       <c r="S42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U42" t="s">
         <v>30</v>
@@ -3263,7 +2482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3286,10 +2505,10 @@
         <v>26</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3303,14 +2522,17 @@
       <c r="N43">
         <v>6</v>
       </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
       <c r="R43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W43">
         <v>3</v>
@@ -3319,7 +2541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3342,16 +2564,16 @@
         <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J44">
         <v>5</v>
       </c>
       <c r="K44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L44">
         <v>8</v>
@@ -3359,11 +2581,14 @@
       <c r="N44">
         <v>0</v>
       </c>
+      <c r="O44">
+        <v>3</v>
+      </c>
       <c r="R44" t="s">
         <v>30</v>
       </c>
       <c r="S44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U44" t="s">
         <v>30</v>
@@ -3375,7 +2600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3398,10 +2623,10 @@
         <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J45">
         <v>-2</v>
@@ -3415,12 +2640,15 @@
       <c r="N45">
         <v>0</v>
       </c>
+      <c r="O45">
+        <v>3</v>
+      </c>
       <c r="R45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S45" t="s">
         <v>35</v>
       </c>
-      <c r="S45" t="s">
-        <v>34</v>
-      </c>
       <c r="U45" t="s">
         <v>30</v>
       </c>
@@ -3434,7 +2662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3457,16 +2685,16 @@
         <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X46">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3474,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3489,28 +2717,28 @@
         <v>26</v>
       </c>
       <c r="H47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I47" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J47">
         <v>-5</v>
       </c>
       <c r="K47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S47" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3518,7 +2746,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3542,7 +2770,7 @@
         <v>4</v>
       </c>
       <c r="K48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L48">
         <v>7</v>
@@ -3551,7 +2779,7 @@
         <v>30</v>
       </c>
       <c r="S48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U48" t="s">
         <v>30</v>
@@ -3560,7 +2788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3568,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -3583,16 +2811,16 @@
         <v>26</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J49">
         <v>4</v>
       </c>
       <c r="K49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L49">
         <v>6</v>
@@ -3600,14 +2828,17 @@
       <c r="N49">
         <v>7</v>
       </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
       <c r="R49" t="s">
         <v>30</v>
       </c>
       <c r="S49" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V49" t="s">
         <v>30</v>
@@ -3616,7 +2847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3624,7 +2855,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -3636,19 +2867,19 @@
         <v>-33</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J50">
         <v>4</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L50">
         <v>7</v>
@@ -3656,11 +2887,14 @@
       <c r="N50">
         <v>4</v>
       </c>
+      <c r="O50">
+        <v>3</v>
+      </c>
       <c r="R50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U50" t="s">
         <v>30</v>
@@ -3669,7 +2903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3692,16 +2926,16 @@
         <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3721,7 +2955,7 @@
         <v>-33</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H52" t="s">
         <v>31</v>
@@ -3733,16 +2967,19 @@
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L52">
         <v>7</v>
       </c>
+      <c r="M52" t="s">
+        <v>73</v>
+      </c>
       <c r="R52" t="s">
         <v>30</v>
       </c>
       <c r="S52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U52" t="s">
         <v>30</v>
@@ -3754,7 +2991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3791,11 +3028,14 @@
       <c r="L53">
         <v>7</v>
       </c>
+      <c r="M53" t="s">
+        <v>29</v>
+      </c>
       <c r="R53" t="s">
         <v>30</v>
       </c>
       <c r="S53" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U53" t="s">
         <v>30</v>
@@ -3807,7 +3047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3830,10 +3070,10 @@
         <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I54" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3847,23 +3087,26 @@
       <c r="N54">
         <v>30</v>
       </c>
+      <c r="O54">
+        <v>9</v>
+      </c>
       <c r="R54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U54" t="s">
         <v>30</v>
       </c>
       <c r="W54" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="X54">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3886,19 +3129,19 @@
         <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X55">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3906,7 +3149,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3936,10 +3179,10 @@
         <v>7</v>
       </c>
       <c r="R56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S56" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U56" t="s">
         <v>30</v>
@@ -3948,7 +3191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3956,7 +3199,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3986,19 +3229,19 @@
         <v>7</v>
       </c>
       <c r="R57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X57">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4006,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -4018,13 +3261,13 @@
         <v>-36</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J58">
         <v>15</v>
@@ -4038,20 +3281,23 @@
       <c r="N58">
         <v>1</v>
       </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
       <c r="R58" t="s">
         <v>30</v>
       </c>
       <c r="S58" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X58">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4059,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -4071,13 +3317,13 @@
         <v>-49</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J59">
         <v>5</v>
@@ -4091,20 +3337,23 @@
       <c r="N59">
         <v>5</v>
       </c>
+      <c r="O59">
+        <v>1</v>
+      </c>
       <c r="R59" t="s">
         <v>30</v>
       </c>
       <c r="S59" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X59">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4112,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -4124,7 +3373,7 @@
         <v>44</v>
       </c>
       <c r="G60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H60" t="s">
         <v>31</v>
@@ -4136,7 +3385,7 @@
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L60">
         <v>6</v>
@@ -4145,7 +3394,7 @@
         <v>30</v>
       </c>
       <c r="S60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U60" t="s">
         <v>30</v>
@@ -4154,7 +3403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4162,7 +3411,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -4174,7 +3423,7 @@
         <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H61" t="s">
         <v>31</v>
@@ -4192,10 +3441,10 @@
         <v>8</v>
       </c>
       <c r="R61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S61" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U61" t="s">
         <v>30</v>
@@ -4204,7 +3453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4212,7 +3461,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -4227,16 +3476,16 @@
         <v>26</v>
       </c>
       <c r="H62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I62" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J62">
         <v>-15</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L62">
         <v>7</v>
@@ -4244,11 +3493,14 @@
       <c r="N62">
         <v>8</v>
       </c>
+      <c r="O62">
+        <v>3</v>
+      </c>
       <c r="R62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S62" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U62" t="s">
         <v>30</v>
@@ -4257,7 +3509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4265,7 +3517,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -4280,10 +3532,10 @@
         <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I63" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J63">
         <v>41</v>
@@ -4297,11 +3549,14 @@
       <c r="N63">
         <v>40</v>
       </c>
+      <c r="O63">
+        <v>9</v>
+      </c>
       <c r="R63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U63" t="s">
         <v>30</v>
@@ -4310,7 +3565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4318,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -4333,10 +3588,10 @@
         <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I64" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J64">
         <v>4</v>
@@ -4350,6 +3605,9 @@
       <c r="N64">
         <v>0</v>
       </c>
+      <c r="O64">
+        <v>3</v>
+      </c>
       <c r="R64" t="s">
         <v>30</v>
       </c>
@@ -4360,7 +3618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4368,7 +3626,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -4386,7 +3644,7 @@
         <v>31</v>
       </c>
       <c r="I65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J65">
         <v>8</v>
@@ -4398,19 +3656,19 @@
         <v>6</v>
       </c>
       <c r="R65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S65" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X65">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4433,16 +3691,16 @@
         <v>26</v>
       </c>
       <c r="H66" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4468,13 +3726,13 @@
         <v>27</v>
       </c>
       <c r="I67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q67">
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4497,10 +3755,10 @@
         <v>30</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I68" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4514,11 +3772,14 @@
       <c r="N68">
         <v>30</v>
       </c>
+      <c r="O68">
+        <v>9</v>
+      </c>
       <c r="R68" t="s">
         <v>30</v>
       </c>
       <c r="S68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U68" t="s">
         <v>30</v>
@@ -4530,7 +3791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4553,10 +3814,10 @@
         <v>30</v>
       </c>
       <c r="H69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I69" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K69" t="s">
         <v>33</v>
@@ -4567,14 +3828,17 @@
       <c r="N69">
         <v>20</v>
       </c>
+      <c r="O69">
+        <v>8</v>
+      </c>
       <c r="R69" t="s">
+        <v>36</v>
+      </c>
+      <c r="S69" t="s">
         <v>35</v>
       </c>
-      <c r="S69" t="s">
-        <v>34</v>
-      </c>
       <c r="U69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W69">
         <v>3</v>
@@ -4583,7 +3847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4591,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -4615,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L70">
         <v>7</v>
@@ -4624,7 +3888,7 @@
         <v>30</v>
       </c>
       <c r="S70" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U70" t="s">
         <v>30</v>
@@ -4633,7 +3897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4641,7 +3905,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4656,37 +3920,43 @@
         <v>26</v>
       </c>
       <c r="H71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J71">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L71">
         <v>6</v>
       </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>1</v>
+      </c>
       <c r="R71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S71" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X71">
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4694,7 +3964,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -4706,19 +3976,19 @@
         <v>-40</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I72" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L72">
         <v>7</v>
@@ -4726,17 +3996,20 @@
       <c r="N72">
         <v>50</v>
       </c>
+      <c r="O72">
+        <v>9</v>
+      </c>
       <c r="R72" t="s">
         <v>30</v>
       </c>
       <c r="S72" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X72">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4756,19 +4029,19 @@
         <v>-41</v>
       </c>
       <c r="G73" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H73" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="X73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4788,19 +4061,19 @@
         <v>49</v>
       </c>
       <c r="G74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J74">
         <v>-5</v>
       </c>
       <c r="K74" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L74">
         <v>6</v>
@@ -4809,7 +4082,7 @@
         <v>30</v>
       </c>
       <c r="S74" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U74" t="s">
         <v>30</v>
@@ -4821,7 +4094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4841,7 +4114,7 @@
         <v>-44</v>
       </c>
       <c r="G75" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H75" t="s">
         <v>31</v>
@@ -4853,16 +4126,19 @@
         <v>3</v>
       </c>
       <c r="K75" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
+      <c r="M75" t="s">
+        <v>34</v>
+      </c>
       <c r="U75" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V75" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W75">
         <v>6</v>
@@ -4871,7 +4147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4891,13 +4167,13 @@
         <v>-40</v>
       </c>
       <c r="G76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H76" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q76">
         <v>23</v>
@@ -4906,7 +4182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4914,7 +4190,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4944,19 +4220,19 @@
         <v>7</v>
       </c>
       <c r="R77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X77">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4964,7 +4240,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4979,25 +4255,25 @@
         <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I78" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J78">
         <v>-5</v>
       </c>
       <c r="K78" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N78">
         <v>7</v>
       </c>
       <c r="R78" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S78" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U78" t="s">
         <v>30</v>
@@ -5006,7 +4282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5014,7 +4290,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -5029,28 +4305,28 @@
         <v>26</v>
       </c>
       <c r="H79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I79" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J79">
         <v>-5</v>
       </c>
       <c r="K79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R79" t="s">
         <v>30</v>
       </c>
       <c r="S79" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="X79">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5058,7 +4334,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -5082,7 +4358,7 @@
         <v>6</v>
       </c>
       <c r="K80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L80">
         <v>8</v>
@@ -5097,7 +4373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5105,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -5120,16 +4396,16 @@
         <v>26</v>
       </c>
       <c r="H81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I81" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L81">
         <v>6</v>
@@ -5137,11 +4413,14 @@
       <c r="N81">
         <v>35</v>
       </c>
+      <c r="O81">
+        <v>9</v>
+      </c>
       <c r="R81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S81" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U81" t="s">
         <v>30</v>
@@ -5150,7 +4429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5173,16 +4452,16 @@
         <v>26</v>
       </c>
       <c r="H82" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X82">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5205,16 +4484,16 @@
         <v>26</v>
       </c>
       <c r="H83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J83">
         <v>12</v>
       </c>
       <c r="K83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L83">
         <v>7</v>
@@ -5222,11 +4501,14 @@
       <c r="N83">
         <v>0</v>
       </c>
+      <c r="O83">
+        <v>3</v>
+      </c>
       <c r="R83" t="s">
         <v>30</v>
       </c>
       <c r="S83" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U83" t="s">
         <v>30</v>
@@ -5238,7 +4520,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5261,25 +4543,25 @@
         <v>30</v>
       </c>
       <c r="H84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I84" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J84">
         <v>6</v>
       </c>
       <c r="K84" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L84">
         <v>7</v>
       </c>
       <c r="R84" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U84" t="s">
         <v>30</v>
@@ -5291,7 +4573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5314,16 +4596,16 @@
         <v>30</v>
       </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J85">
         <v>10</v>
       </c>
       <c r="K85" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L85">
         <v>6</v>
@@ -5331,14 +4613,17 @@
       <c r="N85">
         <v>10</v>
       </c>
+      <c r="O85">
+        <v>5</v>
+      </c>
       <c r="R85" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S85" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U85" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W85">
         <v>6</v>
@@ -5347,7 +4632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5379,16 +4664,19 @@
         <v>12</v>
       </c>
       <c r="K86" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L86">
         <v>7</v>
       </c>
+      <c r="M86" t="s">
+        <v>73</v>
+      </c>
       <c r="R86" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S86" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U86" t="s">
         <v>30</v>
@@ -5400,7 +4688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5432,28 +4720,31 @@
         <v>11</v>
       </c>
       <c r="K87" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L87">
         <v>9</v>
       </c>
+      <c r="M87" t="s">
+        <v>43</v>
+      </c>
       <c r="R87" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S87" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U87" t="s">
         <v>30</v>
       </c>
       <c r="W87" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="X87">
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5476,16 +4767,16 @@
         <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I88" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J88">
         <v>5</v>
       </c>
       <c r="K88" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L88">
         <v>8</v>
@@ -5493,11 +4784,14 @@
       <c r="N88">
         <v>0</v>
       </c>
+      <c r="O88">
+        <v>3</v>
+      </c>
       <c r="R88" t="s">
         <v>30</v>
       </c>
       <c r="S88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U88" t="s">
         <v>30</v>
@@ -5509,7 +4803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5546,20 +4840,23 @@
       <c r="L89">
         <v>8</v>
       </c>
+      <c r="M89" t="s">
+        <v>80</v>
+      </c>
       <c r="R89" t="s">
+        <v>36</v>
+      </c>
+      <c r="S89" t="s">
         <v>35</v>
       </c>
-      <c r="S89" t="s">
-        <v>34</v>
-      </c>
       <c r="U89" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X89">
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5582,16 +4879,16 @@
         <v>26</v>
       </c>
       <c r="H90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I90" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J90">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L90">
         <v>9</v>
@@ -5599,23 +4896,26 @@
       <c r="N90">
         <v>5</v>
       </c>
+      <c r="O90">
+        <v>2</v>
+      </c>
       <c r="R90" t="s">
+        <v>36</v>
+      </c>
+      <c r="S90" t="s">
         <v>35</v>
       </c>
-      <c r="S90" t="s">
-        <v>34</v>
-      </c>
       <c r="U90" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W90" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="X90">
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5638,16 +4938,16 @@
         <v>26</v>
       </c>
       <c r="H91" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I91" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="X91">
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5670,16 +4970,16 @@
         <v>26</v>
       </c>
       <c r="H92" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I92" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X92">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5699,19 +4999,19 @@
         <v>-40</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H93" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I93" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q93">
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5719,7 +5019,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5743,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L94">
         <v>7</v>
@@ -5752,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="S94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U94" t="s">
         <v>30</v>
@@ -5761,7 +5061,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5769,7 +5069,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -5784,10 +5084,10 @@
         <v>26</v>
       </c>
       <c r="H95" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I95" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J95">
         <v>15</v>
@@ -5801,11 +5101,14 @@
       <c r="N95">
         <v>13</v>
       </c>
+      <c r="O95">
+        <v>5</v>
+      </c>
       <c r="R95" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S95" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U95" t="s">
         <v>30</v>
@@ -5814,7 +5117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5822,7 +5125,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5852,19 +5155,19 @@
         <v>8</v>
       </c>
       <c r="R96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S96" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X96">
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5872,7 +5175,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -5902,19 +5205,19 @@
         <v>8</v>
       </c>
       <c r="R97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S97" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X97">
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5922,7 +5225,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5946,16 +5249,16 @@
         <v>-1</v>
       </c>
       <c r="K98" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L98">
         <v>7</v>
       </c>
       <c r="R98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S98" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U98" t="s">
         <v>30</v>
@@ -5964,7 +5267,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5972,7 +5275,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -6005,7 +5308,7 @@
         <v>30</v>
       </c>
       <c r="S99" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U99" t="s">
         <v>30</v>
@@ -6014,7 +5317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="100">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6022,7 +5325,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -6055,7 +5358,7 @@
         <v>30</v>
       </c>
       <c r="S100" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U100" t="s">
         <v>30</v>
@@ -6064,7 +5367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6072,7 +5375,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -6096,7 +5399,7 @@
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L101">
         <v>8</v>
@@ -6105,7 +5408,7 @@
         <v>30</v>
       </c>
       <c r="S101" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U101" t="s">
         <v>30</v>
@@ -6114,7 +5417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="102">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6122,7 +5425,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -6140,7 +5443,7 @@
         <v>31</v>
       </c>
       <c r="I102" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J102">
         <v>6</v>
@@ -6152,10 +5455,10 @@
         <v>10</v>
       </c>
       <c r="R102" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S102" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U102" t="s">
         <v>30</v>
@@ -6164,7 +5467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="103">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6187,16 +5490,16 @@
         <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I103" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="X103">
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6219,16 +5522,16 @@
         <v>26</v>
       </c>
       <c r="H104" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I104" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X104">
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6257,7 +5560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6280,10 +5583,10 @@
         <v>26</v>
       </c>
       <c r="H106" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I106" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J106">
         <v>-5</v>
@@ -6298,7 +5601,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="107">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6335,11 +5638,14 @@
       <c r="L107">
         <v>7</v>
       </c>
+      <c r="M107" t="s">
+        <v>80</v>
+      </c>
       <c r="R107" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S107" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U107" t="s">
         <v>30</v>
@@ -6351,7 +5657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="108">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6374,10 +5680,10 @@
         <v>26</v>
       </c>
       <c r="H108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I108" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6391,11 +5697,14 @@
       <c r="N108">
         <v>5</v>
       </c>
+      <c r="O108">
+        <v>3</v>
+      </c>
       <c r="R108" t="s">
         <v>30</v>
       </c>
       <c r="S108" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U108" t="s">
         <v>30</v>
@@ -6407,7 +5716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="109">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6430,10 +5739,10 @@
         <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I109" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J109">
         <v>-9</v>
@@ -6445,16 +5754,16 @@
         <v>6</v>
       </c>
       <c r="U109" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W109" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="X109">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="110">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6477,16 +5786,16 @@
         <v>26</v>
       </c>
       <c r="H110" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I110" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="X110">
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="111">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6494,7 +5803,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -6506,7 +5815,7 @@
         <v>32</v>
       </c>
       <c r="G111" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H111" t="s">
         <v>31</v>
@@ -6527,16 +5836,16 @@
         <v>30</v>
       </c>
       <c r="S111" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U111" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X111">
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="112">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6544,7 +5853,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -6556,7 +5865,7 @@
         <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H112" t="s">
         <v>31</v>
@@ -6577,7 +5886,7 @@
         <v>30</v>
       </c>
       <c r="S112" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U112" t="s">
         <v>30</v>
@@ -6586,7 +5895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="113">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6594,7 +5903,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -6606,7 +5915,7 @@
         <v>20</v>
       </c>
       <c r="G113" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H113" t="s">
         <v>31</v>
@@ -6627,16 +5936,16 @@
         <v>30</v>
       </c>
       <c r="S113" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U113" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X113">
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="114">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6644,7 +5953,7 @@
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -6656,7 +5965,7 @@
         <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H114" t="s">
         <v>31</v>
@@ -6677,7 +5986,7 @@
         <v>30</v>
       </c>
       <c r="S114" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U114" t="s">
         <v>30</v>
@@ -6686,7 +5995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="115">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6694,7 +6003,7 @@
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -6718,25 +6027,25 @@
         <v>-2</v>
       </c>
       <c r="K115" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L115">
         <v>9</v>
       </c>
       <c r="R115" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S115" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U115" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X115">
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="116">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6759,16 +6068,16 @@
         <v>26</v>
       </c>
       <c r="H116" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I116" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X116">
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="117">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6794,13 +6103,13 @@
         <v>27</v>
       </c>
       <c r="I117" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q117">
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="118">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6837,11 +6146,14 @@
       <c r="L118">
         <v>7</v>
       </c>
+      <c r="M118" t="s">
+        <v>34</v>
+      </c>
       <c r="R118" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S118" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U118" t="s">
         <v>30</v>
@@ -6853,7 +6165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="119">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6876,10 +6188,10 @@
         <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I119" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6893,11 +6205,14 @@
       <c r="N119">
         <v>7</v>
       </c>
+      <c r="O119">
+        <v>3</v>
+      </c>
       <c r="R119" t="s">
         <v>30</v>
       </c>
       <c r="S119" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U119" t="s">
         <v>30</v>
@@ -6909,7 +6224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="120">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6932,10 +6247,10 @@
         <v>26</v>
       </c>
       <c r="H120" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I120" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J120">
         <v>45</v>
@@ -6946,11 +6261,14 @@
       <c r="N120">
         <v>27</v>
       </c>
+      <c r="O120">
+        <v>9</v>
+      </c>
       <c r="R120" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S120" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="U120" t="s">
         <v>30</v>
@@ -6962,7 +6280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="121">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6970,7 +6288,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6982,7 +6300,7 @@
         <v>40</v>
       </c>
       <c r="G121" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H121" t="s">
         <v>31</v>
@@ -7003,16 +6321,16 @@
         <v>30</v>
       </c>
       <c r="S121" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U121" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X121">
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="122">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7020,7 +6338,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -7032,7 +6350,7 @@
         <v>32</v>
       </c>
       <c r="G122" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H122" t="s">
         <v>31</v>
@@ -7053,7 +6371,7 @@
         <v>30</v>
       </c>
       <c r="S122" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U122" t="s">
         <v>30</v>
@@ -7062,7 +6380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="123">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7070,7 +6388,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -7094,16 +6412,16 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L123">
         <v>7</v>
       </c>
       <c r="R123" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S123" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U123" t="s">
         <v>30</v>
@@ -7112,7 +6430,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="124">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7120,7 +6438,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -7135,16 +6453,16 @@
         <v>30</v>
       </c>
       <c r="H124" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I124" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L124">
         <v>7</v>
@@ -7152,20 +6470,23 @@
       <c r="N124">
         <v>14</v>
       </c>
+      <c r="O124">
+        <v>5</v>
+      </c>
       <c r="R124" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S124" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U124" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X124">
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="125">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7173,7 +6494,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D125">
         <v>3</v>
@@ -7197,16 +6518,16 @@
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L125">
         <v>7</v>
       </c>
       <c r="R125" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S125" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U125" t="s">
         <v>30</v>
@@ -7215,7 +6536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="126">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7238,16 +6559,16 @@
         <v>26</v>
       </c>
       <c r="H126" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I126" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X126">
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="127">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7276,7 +6597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="128">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7308,19 +6629,22 @@
         <v>6</v>
       </c>
       <c r="K128" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L128">
         <v>6</v>
       </c>
+      <c r="M128" t="s">
+        <v>73</v>
+      </c>
       <c r="R128" t="s">
         <v>30</v>
       </c>
       <c r="S128" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W128">
         <v>6</v>
@@ -7329,7 +6653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="129">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7349,7 +6673,7 @@
         <v>-26</v>
       </c>
       <c r="G129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H129" t="s">
         <v>31</v>
@@ -7366,12 +6690,15 @@
       <c r="L129">
         <v>7</v>
       </c>
+      <c r="M129" t="s">
+        <v>29</v>
+      </c>
       <c r="R129" t="s">
+        <v>36</v>
+      </c>
+      <c r="S129" t="s">
         <v>35</v>
       </c>
-      <c r="S129" t="s">
-        <v>34</v>
-      </c>
       <c r="U129" t="s">
         <v>30</v>
       </c>
@@ -7382,7 +6709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="130">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7419,12 +6746,15 @@
       <c r="L130">
         <v>6</v>
       </c>
+      <c r="M130" t="s">
+        <v>29</v>
+      </c>
       <c r="R130" t="s">
+        <v>36</v>
+      </c>
+      <c r="S130" t="s">
         <v>35</v>
       </c>
-      <c r="S130" t="s">
-        <v>34</v>
-      </c>
       <c r="U130" t="s">
         <v>30</v>
       </c>
@@ -7435,7 +6765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="131">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7458,16 +6788,16 @@
         <v>30</v>
       </c>
       <c r="H131" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I131" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="X131">
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="132">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7490,16 +6820,16 @@
         <v>30</v>
       </c>
       <c r="H132" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I132" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="X132">
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="133">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7507,7 +6837,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -7537,10 +6867,10 @@
         <v>7</v>
       </c>
       <c r="R133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S133" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U133" t="s">
         <v>30</v>
@@ -7549,7 +6879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="134">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7557,7 +6887,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -7575,25 +6905,25 @@
         <v>31</v>
       </c>
       <c r="I134" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J134">
         <v>-5</v>
       </c>
       <c r="K134" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S134" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="X134">
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="135">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7601,7 +6931,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -7631,19 +6961,19 @@
         <v>7</v>
       </c>
       <c r="R135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S135" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X135">
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="136">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7651,7 +6981,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -7663,7 +6993,7 @@
         <v>30</v>
       </c>
       <c r="G136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H136" t="s">
         <v>31</v>
@@ -7681,19 +7011,19 @@
         <v>8</v>
       </c>
       <c r="R136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S136" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X136">
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="137">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7701,7 +7031,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -7713,7 +7043,7 @@
         <v>17</v>
       </c>
       <c r="G137" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H137" t="s">
         <v>31</v>
@@ -7734,7 +7064,7 @@
         <v>30</v>
       </c>
       <c r="S137" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="U137" t="s">
         <v>30</v>
@@ -7743,7 +7073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="138">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7751,7 +7081,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -7763,7 +7093,7 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H138" t="s">
         <v>31</v>
@@ -7784,7 +7114,7 @@
         <v>30</v>
       </c>
       <c r="S138" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U138" t="s">
         <v>30</v>
@@ -7793,7 +7123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="139">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7801,7 +7131,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -7825,7 +7155,7 @@
         <v>-3</v>
       </c>
       <c r="K139" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L139">
         <v>8</v>
@@ -7834,7 +7164,7 @@
         <v>30</v>
       </c>
       <c r="S139" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U139" t="s">
         <v>30</v>
@@ -7843,7 +7173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="140">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7851,7 +7181,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -7869,22 +7199,22 @@
         <v>31</v>
       </c>
       <c r="I140" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J140">
         <v>-10</v>
       </c>
       <c r="K140" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L140">
         <v>8</v>
       </c>
       <c r="R140" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S140" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="U140" t="s">
         <v>30</v>
@@ -7893,7 +7223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="141">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7901,7 +7231,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -7925,16 +7255,16 @@
         <v>5</v>
       </c>
       <c r="K141" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L141">
         <v>7</v>
       </c>
       <c r="R141" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S141" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U141" t="s">
         <v>30</v>
@@ -7943,7 +7273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="142">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7951,7 +7281,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D142">
         <v>3</v>
@@ -7975,25 +7305,25 @@
         <v>-3</v>
       </c>
       <c r="K142" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L142">
         <v>8</v>
       </c>
       <c r="R142" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S142" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U142" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X142">
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="143">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8016,16 +7346,16 @@
         <v>26</v>
       </c>
       <c r="H143" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I143" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X143">
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="144">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8057,7 +7387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="145">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8080,10 +7410,10 @@
         <v>26</v>
       </c>
       <c r="H145" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I145" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -8097,14 +7427,17 @@
       <c r="N145">
         <v>32</v>
       </c>
+      <c r="O145">
+        <v>8</v>
+      </c>
       <c r="R145" t="s">
         <v>30</v>
       </c>
       <c r="S145" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U145" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W145">
         <v>6</v>
@@ -8113,7 +7446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="146">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8145,16 +7478,19 @@
         <v>9</v>
       </c>
       <c r="K146" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L146">
         <v>6</v>
       </c>
+      <c r="M146" t="s">
+        <v>29</v>
+      </c>
       <c r="R146" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S146" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U146" t="s">
         <v>30</v>
@@ -8166,7 +7502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="147">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8203,11 +7539,14 @@
       <c r="L147">
         <v>7</v>
       </c>
+      <c r="M147" t="s">
+        <v>29</v>
+      </c>
       <c r="R147" t="s">
         <v>30</v>
       </c>
       <c r="S147" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U147" t="s">
         <v>30</v>
@@ -8219,7 +7558,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="148">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8242,16 +7581,16 @@
         <v>26</v>
       </c>
       <c r="H148" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I148" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X148">
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="149">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8259,7 +7598,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -8292,10 +7631,10 @@
         <v>0</v>
       </c>
       <c r="R149" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S149" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U149" t="s">
         <v>30</v>
@@ -8304,7 +7643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="150">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8312,7 +7651,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -8342,10 +7681,10 @@
         <v>7</v>
       </c>
       <c r="R150" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S150" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U150" t="s">
         <v>30</v>
@@ -8354,7 +7693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="151">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8362,7 +7701,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -8386,25 +7725,24 @@
         <v>2</v>
       </c>
       <c r="K151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L151">
         <v>6</v>
       </c>
       <c r="R151" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S151" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U151" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X151">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dowling/dowling-vs-dcg-091126.xlsx
+++ b/Dowling/dowling-vs-dcg-091126.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rc079442b0d4e464e"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Raa5d2b2523434997"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -118,6 +130,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>K GUN</t>
+  </si>
+  <si>
+    <t>PITT</t>
+  </si>
+  <si>
     <t>TWINS WING</t>
   </si>
   <si>
@@ -133,12 +151,30 @@
     <t>N</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>MIAMI</t>
+  </si>
+  <si>
     <t>Y OFF TRIPS PRO</t>
   </si>
   <si>
     <t>WING TRIPS</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
+    <t>STR TEX</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>DUKE</t>
+  </si>
+  <si>
     <t>EMPTY</t>
   </si>
   <si>
@@ -151,18 +187,30 @@
     <t>TRIPS PRO EMPTY</t>
   </si>
   <si>
+    <t>TANGO</t>
+  </si>
+  <si>
     <t>IOWA</t>
   </si>
   <si>
+    <t>WAR</t>
+  </si>
+  <si>
+    <t>G GUN</t>
+  </si>
+  <si>
+    <t>SURF</t>
+  </si>
+  <si>
     <t>Penalty</t>
   </si>
   <si>
+    <t>IOWA ROBBER</t>
+  </si>
+  <si>
     <t>Y TRIPS</t>
   </si>
   <si>
-    <t>IOWA ROBBER</t>
-  </si>
-  <si>
     <t>Punt Rec</t>
   </si>
   <si>
@@ -229,12 +277,21 @@
     <t>Y OFF PRO</t>
   </si>
   <si>
+    <t>G TUCK DOT</t>
+  </si>
+  <si>
     <t>TWINS PRO</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>E-Alley</t>
   </si>
   <si>
+    <t>KNIFE</t>
+  </si>
+  <si>
     <t>DOUBLE WING</t>
   </si>
   <si>
@@ -247,10 +304,22 @@
     <t>KO Rec</t>
   </si>
   <si>
+    <t>FLEX TANGO</t>
+  </si>
+  <si>
+    <t>OMAHA</t>
+  </si>
+  <si>
+    <t>DBL BULLET</t>
+  </si>
+  <si>
     <t>PRO WING</t>
   </si>
   <si>
-    <t>OMAHA</t>
+    <t>OLE MISS</t>
+  </si>
+  <si>
+    <t>STEM</t>
   </si>
   <si>
     <t>A</t>
@@ -272,6 +341,9 @@
   </si>
   <si>
     <t>ACE</t>
+  </si>
+  <si>
+    <t>GUN EVEN</t>
   </si>
   <si>
     <t>TWINS OVER</t>
@@ -290,7 +362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y151"/>
+  <dimension ref="A1:AC151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -368,6 +440,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -377,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -389,13 +473,13 @@
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -406,7 +490,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -418,42 +502,48 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3">
+        <v>38</v>
+      </c>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="W3" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -465,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -477,19 +567,19 @@
         <v>-21</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -500,19 +590,25 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="R4" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-      <c r="X4">
+      <c r="P4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -524,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -536,39 +632,45 @@
         <v>-30</v>
       </c>
       <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L5">
         <v>7</v>
       </c>
       <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
         <v>29</v>
       </c>
-      <c r="R5" t="s">
-        <v>36</v>
-      </c>
-      <c r="S5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" t="s">
-        <v>36</v>
-      </c>
-      <c r="W5">
-        <v>3</v>
-      </c>
-      <c r="X5">
+      <c r="Q5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -580,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -592,42 +694,48 @@
         <v>-34</v>
       </c>
       <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>7</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" t="s">
-        <v>35</v>
-      </c>
-      <c r="U6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" t="s">
-        <v>30</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
-      <c r="X6">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="W6" t="s">
+        <v>42</v>
+      </c>
+      <c r="X6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -639,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -651,19 +759,19 @@
         <v>-35</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J7">
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -674,22 +782,28 @@
       <c r="O7">
         <v>3</v>
       </c>
-      <c r="R7" t="s">
-        <v>30</v>
-      </c>
-      <c r="S7" t="s">
-        <v>42</v>
-      </c>
-      <c r="U7" t="s">
-        <v>36</v>
-      </c>
-      <c r="V7" t="s">
-        <v>30</v>
-      </c>
-      <c r="W7">
+      <c r="P7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S7">
         <v>6</v>
       </c>
-      <c r="X7">
+      <c r="W7" t="s">
+        <v>34</v>
+      </c>
+      <c r="X7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -701,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -713,19 +827,19 @@
         <v>-43</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -736,19 +850,25 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="R8" t="s">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U8" t="s">
-        <v>36</v>
-      </c>
-      <c r="W8">
-        <v>3</v>
-      </c>
-      <c r="X8">
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="W8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -760,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -772,20 +892,20 @@
         <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
         <v>37</v>
       </c>
-      <c r="I9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
       <c r="L9">
         <v>7</v>
       </c>
@@ -795,19 +915,25 @@
       <c r="O9">
         <v>1</v>
       </c>
-      <c r="R9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S9" t="s">
-        <v>41</v>
-      </c>
-      <c r="U9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9">
-        <v>3</v>
-      </c>
-      <c r="X9">
+      <c r="P9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>47</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="W9" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -819,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -831,19 +957,19 @@
         <v>-41</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -854,19 +980,25 @@
       <c r="O10">
         <v>3</v>
       </c>
-      <c r="R10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U10" t="s">
-        <v>30</v>
-      </c>
-      <c r="W10">
-        <v>3</v>
-      </c>
-      <c r="X10">
+      <c r="P10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10">
+        <v>3</v>
+      </c>
+      <c r="W10" t="s">
+        <v>34</v>
+      </c>
+      <c r="X10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -878,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -890,36 +1022,42 @@
         <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
       <c r="M11" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" t="s">
-        <v>30</v>
-      </c>
-      <c r="U11" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11">
-        <v>3</v>
-      </c>
-      <c r="X11">
+        <v>55</v>
+      </c>
+      <c r="P11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>47</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="W11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -931,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -943,19 +1081,19 @@
         <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -966,22 +1104,28 @@
       <c r="O12">
         <v>7</v>
       </c>
-      <c r="R12" t="s">
-        <v>36</v>
-      </c>
-      <c r="S12" t="s">
-        <v>45</v>
-      </c>
-      <c r="U12" t="s">
-        <v>36</v>
-      </c>
-      <c r="V12" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12">
-        <v>3</v>
-      </c>
-      <c r="X12">
+      <c r="P12" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>47</v>
+      </c>
+      <c r="S12">
+        <v>3</v>
+      </c>
+      <c r="W12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -993,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1005,19 +1149,19 @@
         <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -1028,19 +1172,28 @@
       <c r="O13">
         <v>6</v>
       </c>
+      <c r="P13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>47</v>
+      </c>
       <c r="R13" t="s">
-        <v>30</v>
-      </c>
-      <c r="S13" t="s">
-        <v>40</v>
-      </c>
-      <c r="U13" t="s">
-        <v>30</v>
-      </c>
-      <c r="W13">
-        <v>3</v>
-      </c>
-      <c r="X13">
+        <v>58</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="W13" t="s">
+        <v>34</v>
+      </c>
+      <c r="X13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -1052,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1064,19 +1217,19 @@
         <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J14">
         <v>12</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1087,19 +1240,28 @@
       <c r="O14">
         <v>4</v>
       </c>
-      <c r="R14" t="s">
-        <v>30</v>
+      <c r="P14" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>47</v>
       </c>
       <c r="S14" t="s">
-        <v>41</v>
-      </c>
-      <c r="U14" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="T14" t="s">
+        <v>60</v>
       </c>
       <c r="W14" t="s">
-        <v>46</v>
-      </c>
-      <c r="X14">
+        <v>34</v>
+      </c>
+      <c r="X14" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -1111,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1123,39 +1285,45 @@
         <v>31</v>
       </c>
       <c r="G15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
         <v>36</v>
-      </c>
-      <c r="H15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" t="s">
-        <v>32</v>
       </c>
       <c r="J15">
         <v>-2</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L15">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" t="s">
-        <v>36</v>
-      </c>
-      <c r="S15" t="s">
-        <v>41</v>
-      </c>
-      <c r="U15" t="s">
-        <v>36</v>
-      </c>
-      <c r="W15">
-        <v>3</v>
-      </c>
-      <c r="X15">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15">
+        <v>3</v>
+      </c>
+      <c r="W15" t="s">
+        <v>42</v>
+      </c>
+      <c r="X15" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -1167,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1179,39 +1347,45 @@
         <v>33</v>
       </c>
       <c r="G16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
         <v>36</v>
       </c>
-      <c r="H16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" t="s">
-        <v>32</v>
-      </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16">
+        <v>7</v>
+      </c>
+      <c r="M16" t="s">
         <v>33</v>
       </c>
-      <c r="L16">
-        <v>7</v>
-      </c>
-      <c r="M16" t="s">
-        <v>29</v>
-      </c>
-      <c r="R16" t="s">
-        <v>30</v>
-      </c>
-      <c r="S16" t="s">
-        <v>35</v>
-      </c>
-      <c r="U16" t="s">
-        <v>36</v>
-      </c>
-      <c r="W16">
+      <c r="P16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>62</v>
+      </c>
+      <c r="S16">
         <v>6</v>
       </c>
-      <c r="X16">
+      <c r="W16" t="s">
+        <v>34</v>
+      </c>
+      <c r="X16" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1223,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1235,21 +1409,27 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I17" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J17">
         <v>-5</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
-      </c>
-      <c r="W17">
-        <v>3</v>
-      </c>
-      <c r="X17">
+        <v>37</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>47</v>
+      </c>
+      <c r="R17" t="s">
+        <v>58</v>
+      </c>
+      <c r="S17">
+        <v>3</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1261,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1273,19 +1453,19 @@
         <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -1296,19 +1476,25 @@
       <c r="O18">
         <v>8</v>
       </c>
-      <c r="R18" t="s">
-        <v>36</v>
+      <c r="P18" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>53</v>
       </c>
       <c r="S18" t="s">
-        <v>48</v>
-      </c>
-      <c r="U18" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="W18" t="s">
-        <v>49</v>
-      </c>
-      <c r="X18">
+        <v>42</v>
+      </c>
+      <c r="X18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1320,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -1332,15 +1518,15 @@
         <v>37</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
-      </c>
-      <c r="X19">
+        <v>67</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1352,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1364,39 +1550,42 @@
         <v>-7</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
-      <c r="R20" t="s">
-        <v>30</v>
-      </c>
-      <c r="S20" t="s">
-        <v>53</v>
-      </c>
-      <c r="T20" t="s">
-        <v>54</v>
-      </c>
-      <c r="U20" t="s">
-        <v>30</v>
-      </c>
-      <c r="V20" t="s">
-        <v>30</v>
-      </c>
-      <c r="X20">
+      <c r="P20" t="s">
+        <v>50</v>
+      </c>
+      <c r="W20" t="s">
+        <v>34</v>
+      </c>
+      <c r="X20" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB20">
         <v>1</v>
       </c>
     </row>
@@ -1408,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1420,36 +1609,39 @@
         <v>-7</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J21">
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
-      <c r="R21" t="s">
-        <v>55</v>
-      </c>
-      <c r="S21" t="s">
-        <v>56</v>
-      </c>
-      <c r="T21" t="s">
-        <v>57</v>
-      </c>
-      <c r="U21" t="s">
-        <v>30</v>
-      </c>
-      <c r="X21">
+      <c r="P21" t="s">
+        <v>50</v>
+      </c>
+      <c r="W21" t="s">
+        <v>71</v>
+      </c>
+      <c r="X21" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21">
         <v>1</v>
       </c>
     </row>
@@ -1461,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1473,19 +1665,19 @@
         <v>-13</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
         <v>37</v>
-      </c>
-      <c r="I22" t="s">
-        <v>38</v>
-      </c>
-      <c r="J22">
-        <v>10</v>
-      </c>
-      <c r="K22" t="s">
-        <v>33</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -1496,19 +1688,22 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="R22" t="s">
-        <v>36</v>
-      </c>
-      <c r="S22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T22" t="s">
-        <v>59</v>
-      </c>
-      <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="X22">
+      <c r="P22" t="s">
+        <v>50</v>
+      </c>
+      <c r="W22" t="s">
+        <v>42</v>
+      </c>
+      <c r="X22" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB22">
         <v>1</v>
       </c>
     </row>
@@ -1520,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1532,19 +1727,19 @@
         <v>-23</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -1555,16 +1750,19 @@
       <c r="O23">
         <v>2</v>
       </c>
-      <c r="R23" t="s">
-        <v>30</v>
-      </c>
-      <c r="S23" t="s">
-        <v>60</v>
-      </c>
-      <c r="U23" t="s">
-        <v>30</v>
-      </c>
-      <c r="X23">
+      <c r="P23" t="s">
+        <v>50</v>
+      </c>
+      <c r="W23" t="s">
+        <v>34</v>
+      </c>
+      <c r="X23" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23">
         <v>1</v>
       </c>
     </row>
@@ -1576,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1588,19 +1786,19 @@
         <v>-23</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -1611,16 +1809,19 @@
       <c r="O24">
         <v>2</v>
       </c>
-      <c r="R24" t="s">
-        <v>30</v>
-      </c>
-      <c r="S24" t="s">
-        <v>42</v>
-      </c>
-      <c r="U24" t="s">
-        <v>30</v>
-      </c>
-      <c r="X24">
+      <c r="P24" t="s">
+        <v>52</v>
+      </c>
+      <c r="W24" t="s">
+        <v>34</v>
+      </c>
+      <c r="X24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB24">
         <v>1</v>
       </c>
     </row>
@@ -1632,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1644,33 +1845,36 @@
         <v>-23</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="J25">
         <v>-10</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L25">
         <v>6</v>
       </c>
-      <c r="R25" t="s">
-        <v>30</v>
-      </c>
-      <c r="S25" t="s">
-        <v>62</v>
-      </c>
-      <c r="U25" t="s">
-        <v>30</v>
-      </c>
-      <c r="X25">
+      <c r="P25" t="s">
+        <v>50</v>
+      </c>
+      <c r="W25" t="s">
+        <v>34</v>
+      </c>
+      <c r="X25" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB25">
         <v>1</v>
       </c>
     </row>
@@ -1682,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -1694,15 +1898,15 @@
         <v>-13</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s">
-        <v>51</v>
-      </c>
-      <c r="X26">
+        <v>67</v>
+      </c>
+      <c r="AB26">
         <v>1</v>
       </c>
     </row>
@@ -1714,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1726,39 +1930,45 @@
         <v>-33</v>
       </c>
       <c r="G27" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
         <v>36</v>
-      </c>
-      <c r="H27" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" t="s">
-        <v>32</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L27">
         <v>7</v>
       </c>
       <c r="M27" t="s">
-        <v>43</v>
-      </c>
-      <c r="R27" t="s">
-        <v>36</v>
-      </c>
-      <c r="S27" t="s">
-        <v>48</v>
-      </c>
-      <c r="U27" t="s">
-        <v>36</v>
-      </c>
-      <c r="W27">
-        <v>3</v>
-      </c>
-      <c r="X27">
+        <v>55</v>
+      </c>
+      <c r="P27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>40</v>
+      </c>
+      <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="W27" t="s">
+        <v>42</v>
+      </c>
+      <c r="X27" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1770,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1782,27 +1992,33 @@
         <v>-32</v>
       </c>
       <c r="G28" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J28">
         <v>-5</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" t="s">
-        <v>30</v>
-      </c>
-      <c r="S28" t="s">
-        <v>64</v>
-      </c>
-      <c r="X28">
+        <v>37</v>
+      </c>
+      <c r="P28" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>40</v>
+      </c>
+      <c r="W28" t="s">
+        <v>34</v>
+      </c>
+      <c r="X28" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1814,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -1826,39 +2042,45 @@
         <v>-27</v>
       </c>
       <c r="G29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" t="s">
         <v>36</v>
       </c>
-      <c r="H29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" t="s">
-        <v>32</v>
-      </c>
       <c r="J29">
         <v>2</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L29">
         <v>7</v>
       </c>
       <c r="M29" t="s">
-        <v>43</v>
-      </c>
-      <c r="R29" t="s">
-        <v>30</v>
-      </c>
-      <c r="S29" t="s">
-        <v>40</v>
-      </c>
-      <c r="U29" t="s">
-        <v>36</v>
-      </c>
-      <c r="W29">
-        <v>3</v>
-      </c>
-      <c r="X29">
+        <v>55</v>
+      </c>
+      <c r="P29" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>47</v>
+      </c>
+      <c r="S29">
+        <v>3</v>
+      </c>
+      <c r="W29" t="s">
+        <v>34</v>
+      </c>
+      <c r="X29" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1870,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -1882,19 +2104,19 @@
         <v>-29</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -1905,16 +2127,22 @@
       <c r="O30">
         <v>3</v>
       </c>
-      <c r="R30" t="s">
-        <v>36</v>
-      </c>
-      <c r="U30" t="s">
-        <v>30</v>
-      </c>
-      <c r="W30">
+      <c r="P30" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>53</v>
+      </c>
+      <c r="S30">
         <v>6</v>
       </c>
-      <c r="X30">
+      <c r="W30" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1926,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -1938,15 +2166,15 @@
         <v>-29</v>
       </c>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>65</v>
-      </c>
-      <c r="X31">
+        <v>81</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1958,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1970,19 +2198,19 @@
         <v>-44</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I32" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J32">
         <v>8</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -1993,16 +2221,19 @@
       <c r="O32">
         <v>2</v>
       </c>
-      <c r="R32" t="s">
-        <v>36</v>
-      </c>
-      <c r="S32" t="s">
-        <v>66</v>
-      </c>
-      <c r="U32" t="s">
-        <v>36</v>
-      </c>
-      <c r="X32">
+      <c r="P32" t="s">
+        <v>61</v>
+      </c>
+      <c r="W32" t="s">
+        <v>42</v>
+      </c>
+      <c r="X32" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
     </row>
@@ -2014,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2026,33 +2257,36 @@
         <v>48</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J33">
         <v>11</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
-      <c r="R33" t="s">
-        <v>36</v>
-      </c>
-      <c r="S33" t="s">
-        <v>40</v>
-      </c>
-      <c r="U33" t="s">
-        <v>36</v>
-      </c>
-      <c r="X33">
+      <c r="P33" t="s">
+        <v>50</v>
+      </c>
+      <c r="W33" t="s">
+        <v>42</v>
+      </c>
+      <c r="X33" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB33">
         <v>2</v>
       </c>
     </row>
@@ -2064,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2076,30 +2310,33 @@
         <v>37</v>
       </c>
       <c r="G34" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34" t="s">
         <v>36</v>
-      </c>
-      <c r="H34" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" t="s">
-        <v>32</v>
       </c>
       <c r="J34">
         <v>16</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L34">
         <v>6</v>
       </c>
-      <c r="R34" t="s">
-        <v>30</v>
-      </c>
-      <c r="U34" t="s">
-        <v>30</v>
-      </c>
-      <c r="X34">
+      <c r="P34" t="s">
+        <v>61</v>
+      </c>
+      <c r="W34" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB34">
         <v>2</v>
       </c>
     </row>
@@ -2111,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2123,19 +2360,19 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J35">
         <v>5</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L35">
         <v>6</v>
@@ -2146,13 +2383,16 @@
       <c r="O35">
         <v>1</v>
       </c>
-      <c r="R35" t="s">
-        <v>30</v>
-      </c>
-      <c r="U35" t="s">
-        <v>36</v>
-      </c>
-      <c r="X35">
+      <c r="P35" t="s">
+        <v>61</v>
+      </c>
+      <c r="W35" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB35">
         <v>2</v>
       </c>
     </row>
@@ -2164,7 +2404,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2176,33 +2416,36 @@
         <v>16</v>
       </c>
       <c r="G36" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36" t="s">
         <v>36</v>
       </c>
-      <c r="H36" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" t="s">
-        <v>32</v>
-      </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L36">
         <v>7</v>
       </c>
-      <c r="R36" t="s">
-        <v>30</v>
-      </c>
-      <c r="S36" t="s">
-        <v>66</v>
-      </c>
-      <c r="U36" t="s">
-        <v>30</v>
-      </c>
-      <c r="X36">
+      <c r="P36" t="s">
+        <v>61</v>
+      </c>
+      <c r="W36" t="s">
+        <v>34</v>
+      </c>
+      <c r="X36" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB36">
         <v>2</v>
       </c>
     </row>
@@ -2214,7 +2457,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -2226,33 +2469,36 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I37" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="J37">
         <v>12</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L37">
         <v>7</v>
       </c>
-      <c r="R37" t="s">
-        <v>55</v>
-      </c>
-      <c r="S37" t="s">
-        <v>56</v>
-      </c>
-      <c r="U37" t="s">
-        <v>30</v>
-      </c>
-      <c r="X37">
+      <c r="P37" t="s">
+        <v>50</v>
+      </c>
+      <c r="W37" t="s">
+        <v>71</v>
+      </c>
+      <c r="X37" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB37">
         <v>2</v>
       </c>
     </row>
@@ -2264,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2276,33 +2522,36 @@
         <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I38" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L38">
         <v>9</v>
       </c>
-      <c r="R38" t="s">
-        <v>55</v>
-      </c>
-      <c r="S38" t="s">
-        <v>56</v>
-      </c>
-      <c r="U38" t="s">
-        <v>30</v>
-      </c>
-      <c r="X38">
+      <c r="P38" t="s">
+        <v>50</v>
+      </c>
+      <c r="W38" t="s">
+        <v>71</v>
+      </c>
+      <c r="X38" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB38">
         <v>2</v>
       </c>
     </row>
@@ -2314,7 +2563,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2326,15 +2575,15 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>70</v>
-      </c>
-      <c r="X39">
+        <v>86</v>
+      </c>
+      <c r="AB39">
         <v>2</v>
       </c>
     </row>
@@ -2346,7 +2595,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2358,13 +2607,13 @@
         <v>-40</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -2375,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2387,19 +2636,19 @@
         <v>-20</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H41" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I41" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J41">
         <v>8</v>
       </c>
       <c r="K41" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L41">
         <v>7</v>
@@ -2410,19 +2659,25 @@
       <c r="O41">
         <v>2</v>
       </c>
-      <c r="R41" t="s">
-        <v>36</v>
-      </c>
-      <c r="S41" t="s">
-        <v>35</v>
-      </c>
-      <c r="U41" t="s">
-        <v>36</v>
-      </c>
-      <c r="W41">
-        <v>3</v>
-      </c>
-      <c r="X41">
+      <c r="P41" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>47</v>
+      </c>
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="W41" t="s">
+        <v>42</v>
+      </c>
+      <c r="X41" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2434,7 +2689,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2446,39 +2701,45 @@
         <v>-28</v>
       </c>
       <c r="G42" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" t="s">
         <v>36</v>
       </c>
-      <c r="H42" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" t="s">
-        <v>32</v>
-      </c>
       <c r="J42">
         <v>4</v>
       </c>
       <c r="K42" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42" t="s">
-        <v>29</v>
-      </c>
-      <c r="R42" t="s">
-        <v>30</v>
-      </c>
-      <c r="S42" t="s">
-        <v>64</v>
-      </c>
-      <c r="U42" t="s">
-        <v>30</v>
-      </c>
-      <c r="W42">
-        <v>3</v>
-      </c>
-      <c r="X42">
+        <v>33</v>
+      </c>
+      <c r="P42" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>40</v>
+      </c>
+      <c r="S42">
+        <v>3</v>
+      </c>
+      <c r="W42" t="s">
+        <v>34</v>
+      </c>
+      <c r="X42" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2490,7 +2751,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2502,19 +2763,19 @@
         <v>-32</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I43" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L43">
         <v>6</v>
@@ -2525,19 +2786,25 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="R43" t="s">
-        <v>36</v>
-      </c>
-      <c r="S43" t="s">
-        <v>64</v>
-      </c>
-      <c r="U43" t="s">
-        <v>36</v>
-      </c>
-      <c r="W43">
-        <v>3</v>
-      </c>
-      <c r="X43">
+      <c r="P43" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>47</v>
+      </c>
+      <c r="S43">
+        <v>3</v>
+      </c>
+      <c r="W43" t="s">
+        <v>42</v>
+      </c>
+      <c r="X43" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2549,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -2561,19 +2828,19 @@
         <v>-32</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I44" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J44">
         <v>5</v>
       </c>
       <c r="K44" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L44">
         <v>8</v>
@@ -2584,19 +2851,28 @@
       <c r="O44">
         <v>3</v>
       </c>
+      <c r="P44" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>47</v>
+      </c>
       <c r="R44" t="s">
-        <v>30</v>
-      </c>
-      <c r="S44" t="s">
-        <v>41</v>
-      </c>
-      <c r="U44" t="s">
-        <v>30</v>
-      </c>
-      <c r="W44">
-        <v>3</v>
-      </c>
-      <c r="X44">
+        <v>51</v>
+      </c>
+      <c r="S44">
+        <v>3</v>
+      </c>
+      <c r="W44" t="s">
+        <v>34</v>
+      </c>
+      <c r="X44" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2608,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -2620,19 +2896,19 @@
         <v>-37</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H45" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J45">
         <v>-2</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L45">
         <v>7</v>
@@ -2643,22 +2919,28 @@
       <c r="O45">
         <v>3</v>
       </c>
-      <c r="R45" t="s">
-        <v>36</v>
-      </c>
-      <c r="S45" t="s">
-        <v>35</v>
-      </c>
-      <c r="U45" t="s">
-        <v>30</v>
-      </c>
-      <c r="V45" t="s">
-        <v>30</v>
-      </c>
-      <c r="W45">
-        <v>3</v>
-      </c>
-      <c r="X45">
+      <c r="P45" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>47</v>
+      </c>
+      <c r="S45">
+        <v>3</v>
+      </c>
+      <c r="W45" t="s">
+        <v>42</v>
+      </c>
+      <c r="X45" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB45">
         <v>3</v>
       </c>
     </row>
@@ -2670,7 +2952,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2682,15 +2964,15 @@
         <v>-35</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H46" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I46" t="s">
-        <v>65</v>
-      </c>
-      <c r="X46">
+        <v>81</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -2702,7 +2984,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2714,27 +2996,30 @@
         <v>-30</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I47" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J47">
         <v>-5</v>
       </c>
       <c r="K47" t="s">
-        <v>39</v>
-      </c>
-      <c r="R47" t="s">
-        <v>36</v>
-      </c>
-      <c r="S47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X47">
+        <v>45</v>
+      </c>
+      <c r="P47" t="s">
+        <v>50</v>
+      </c>
+      <c r="W47" t="s">
+        <v>42</v>
+      </c>
+      <c r="X47" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2746,7 +3031,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2758,33 +3043,36 @@
         <v>-25</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J48">
         <v>4</v>
       </c>
       <c r="K48" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L48">
         <v>7</v>
       </c>
-      <c r="R48" t="s">
-        <v>30</v>
-      </c>
-      <c r="S48" t="s">
-        <v>72</v>
-      </c>
-      <c r="U48" t="s">
-        <v>30</v>
-      </c>
-      <c r="X48">
+      <c r="P48" t="s">
+        <v>88</v>
+      </c>
+      <c r="W48" t="s">
+        <v>34</v>
+      </c>
+      <c r="X48" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -2796,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2808,19 +3096,19 @@
         <v>-29</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I49" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J49">
         <v>4</v>
       </c>
       <c r="K49" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L49">
         <v>6</v>
@@ -2831,19 +3119,22 @@
       <c r="O49">
         <v>1</v>
       </c>
-      <c r="R49" t="s">
-        <v>30</v>
-      </c>
-      <c r="S49" t="s">
-        <v>60</v>
-      </c>
-      <c r="U49" t="s">
-        <v>36</v>
-      </c>
-      <c r="V49" t="s">
-        <v>30</v>
-      </c>
-      <c r="X49">
+      <c r="P49" t="s">
+        <v>61</v>
+      </c>
+      <c r="W49" t="s">
+        <v>34</v>
+      </c>
+      <c r="X49" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2855,7 +3146,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2867,19 +3158,19 @@
         <v>-33</v>
       </c>
       <c r="G50" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H50" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J50">
         <v>4</v>
       </c>
       <c r="K50" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L50">
         <v>7</v>
@@ -2890,16 +3181,19 @@
       <c r="O50">
         <v>3</v>
       </c>
-      <c r="R50" t="s">
-        <v>55</v>
-      </c>
-      <c r="S50" t="s">
-        <v>56</v>
-      </c>
-      <c r="U50" t="s">
-        <v>30</v>
-      </c>
-      <c r="X50">
+      <c r="P50" t="s">
+        <v>90</v>
+      </c>
+      <c r="W50" t="s">
+        <v>71</v>
+      </c>
+      <c r="X50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2911,7 +3205,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2923,15 +3217,15 @@
         <v>-37</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I51" t="s">
-        <v>65</v>
-      </c>
-      <c r="X51">
+        <v>81</v>
+      </c>
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2943,7 +3237,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2955,39 +3249,45 @@
         <v>-33</v>
       </c>
       <c r="G52" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s">
         <v>36</v>
       </c>
-      <c r="H52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" t="s">
-        <v>32</v>
-      </c>
       <c r="J52">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L52">
         <v>7</v>
       </c>
       <c r="M52" t="s">
-        <v>73</v>
-      </c>
-      <c r="R52" t="s">
-        <v>30</v>
-      </c>
-      <c r="S52" t="s">
-        <v>35</v>
-      </c>
-      <c r="U52" t="s">
-        <v>30</v>
-      </c>
-      <c r="W52">
-        <v>3</v>
-      </c>
-      <c r="X52">
+        <v>91</v>
+      </c>
+      <c r="P52" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>47</v>
+      </c>
+      <c r="S52">
+        <v>3</v>
+      </c>
+      <c r="W52" t="s">
+        <v>34</v>
+      </c>
+      <c r="X52" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB52">
         <v>4</v>
       </c>
     </row>
@@ -2999,7 +3299,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -3011,39 +3311,45 @@
         <v>-40</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53" t="s">
+        <v>37</v>
+      </c>
+      <c r="L53">
+        <v>7</v>
+      </c>
+      <c r="M53" t="s">
         <v>33</v>
       </c>
-      <c r="L53">
-        <v>7</v>
-      </c>
-      <c r="M53" t="s">
-        <v>29</v>
-      </c>
-      <c r="R53" t="s">
-        <v>30</v>
-      </c>
-      <c r="S53" t="s">
-        <v>66</v>
-      </c>
-      <c r="U53" t="s">
-        <v>30</v>
-      </c>
-      <c r="W53">
-        <v>3</v>
-      </c>
-      <c r="X53">
+      <c r="P53" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>47</v>
+      </c>
+      <c r="S53">
+        <v>3</v>
+      </c>
+      <c r="W53" t="s">
+        <v>34</v>
+      </c>
+      <c r="X53" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB53">
         <v>4</v>
       </c>
     </row>
@@ -3055,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -3067,19 +3373,19 @@
         <v>-40</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H54" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I54" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L54">
         <v>8</v>
@@ -3090,19 +3396,28 @@
       <c r="O54">
         <v>9</v>
       </c>
-      <c r="R54" t="s">
-        <v>36</v>
+      <c r="P54" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>47</v>
       </c>
       <c r="S54" t="s">
-        <v>41</v>
-      </c>
-      <c r="U54" t="s">
-        <v>30</v>
+        <v>59</v>
+      </c>
+      <c r="T54" t="s">
+        <v>92</v>
       </c>
       <c r="W54" t="s">
-        <v>46</v>
-      </c>
-      <c r="X54">
+        <v>42</v>
+      </c>
+      <c r="X54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -3114,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -3126,18 +3441,18 @@
         <v>-40</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H55" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I55" t="s">
-        <v>51</v>
-      </c>
-      <c r="V55" t="s">
-        <v>36</v>
-      </c>
-      <c r="X55">
+        <v>67</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -3149,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3161,33 +3476,36 @@
         <v>-23</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J56">
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L56">
         <v>7</v>
       </c>
-      <c r="R56" t="s">
-        <v>36</v>
-      </c>
-      <c r="S56" t="s">
-        <v>40</v>
-      </c>
-      <c r="U56" t="s">
-        <v>30</v>
-      </c>
-      <c r="X56">
+      <c r="P56" t="s">
+        <v>50</v>
+      </c>
+      <c r="W56" t="s">
+        <v>42</v>
+      </c>
+      <c r="X56" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB56">
         <v>4</v>
       </c>
     </row>
@@ -3199,7 +3517,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3211,33 +3529,36 @@
         <v>-27</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J57">
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L57">
         <v>7</v>
       </c>
-      <c r="R57" t="s">
-        <v>36</v>
-      </c>
-      <c r="S57" t="s">
-        <v>40</v>
-      </c>
-      <c r="U57" t="s">
-        <v>36</v>
-      </c>
-      <c r="X57">
+      <c r="P57" t="s">
+        <v>50</v>
+      </c>
+      <c r="W57" t="s">
+        <v>42</v>
+      </c>
+      <c r="X57" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
     </row>
@@ -3249,7 +3570,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3261,19 +3582,19 @@
         <v>-36</v>
       </c>
       <c r="G58" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H58" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I58" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J58">
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L58">
         <v>7</v>
@@ -3284,16 +3605,19 @@
       <c r="O58">
         <v>1</v>
       </c>
-      <c r="R58" t="s">
-        <v>30</v>
-      </c>
-      <c r="S58" t="s">
-        <v>66</v>
-      </c>
-      <c r="U58" t="s">
-        <v>36</v>
-      </c>
-      <c r="X58">
+      <c r="P58" t="s">
+        <v>39</v>
+      </c>
+      <c r="W58" t="s">
+        <v>34</v>
+      </c>
+      <c r="X58" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
     </row>
@@ -3305,7 +3629,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3317,19 +3641,19 @@
         <v>-49</v>
       </c>
       <c r="G59" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H59" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I59" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J59">
         <v>5</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L59">
         <v>6</v>
@@ -3340,16 +3664,19 @@
       <c r="O59">
         <v>1</v>
       </c>
-      <c r="R59" t="s">
-        <v>30</v>
-      </c>
-      <c r="S59" t="s">
-        <v>62</v>
-      </c>
-      <c r="U59" t="s">
-        <v>36</v>
-      </c>
-      <c r="X59">
+      <c r="P59" t="s">
+        <v>61</v>
+      </c>
+      <c r="W59" t="s">
+        <v>34</v>
+      </c>
+      <c r="X59" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -3361,7 +3688,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3373,33 +3700,36 @@
         <v>44</v>
       </c>
       <c r="G60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60" t="s">
         <v>36</v>
       </c>
-      <c r="H60" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" t="s">
-        <v>32</v>
-      </c>
       <c r="J60">
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L60">
         <v>6</v>
       </c>
-      <c r="R60" t="s">
-        <v>30</v>
-      </c>
-      <c r="S60" t="s">
-        <v>62</v>
-      </c>
-      <c r="U60" t="s">
-        <v>30</v>
-      </c>
-      <c r="X60">
+      <c r="P60" t="s">
+        <v>50</v>
+      </c>
+      <c r="W60" t="s">
+        <v>34</v>
+      </c>
+      <c r="X60" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -3411,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -3423,33 +3753,36 @@
         <v>42</v>
       </c>
       <c r="G61" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61" t="s">
         <v>36</v>
       </c>
-      <c r="H61" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" t="s">
-        <v>32</v>
-      </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L61">
         <v>8</v>
       </c>
-      <c r="R61" t="s">
-        <v>55</v>
-      </c>
-      <c r="S61" t="s">
-        <v>74</v>
-      </c>
-      <c r="U61" t="s">
-        <v>30</v>
-      </c>
-      <c r="X61">
+      <c r="P61" t="s">
+        <v>50</v>
+      </c>
+      <c r="W61" t="s">
+        <v>71</v>
+      </c>
+      <c r="X61" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -3461,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3473,19 +3806,19 @@
         <v>38</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I62" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J62">
         <v>-15</v>
       </c>
       <c r="K62" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L62">
         <v>7</v>
@@ -3496,16 +3829,19 @@
       <c r="O62">
         <v>3</v>
       </c>
-      <c r="R62" t="s">
-        <v>36</v>
-      </c>
-      <c r="S62" t="s">
-        <v>66</v>
-      </c>
-      <c r="U62" t="s">
-        <v>30</v>
-      </c>
-      <c r="X62">
+      <c r="P62" t="s">
+        <v>39</v>
+      </c>
+      <c r="W62" t="s">
+        <v>42</v>
+      </c>
+      <c r="X62" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB62">
         <v>4</v>
       </c>
     </row>
@@ -3517,7 +3853,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -3529,19 +3865,19 @@
         <v>-47</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H63" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I63" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J63">
         <v>41</v>
       </c>
       <c r="K63" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L63">
         <v>6</v>
@@ -3552,16 +3888,19 @@
       <c r="O63">
         <v>9</v>
       </c>
-      <c r="R63" t="s">
-        <v>36</v>
-      </c>
-      <c r="S63" t="s">
-        <v>58</v>
-      </c>
-      <c r="U63" t="s">
-        <v>30</v>
-      </c>
-      <c r="X63">
+      <c r="P63" t="s">
+        <v>50</v>
+      </c>
+      <c r="W63" t="s">
+        <v>42</v>
+      </c>
+      <c r="X63" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB63">
         <v>4</v>
       </c>
     </row>
@@ -3573,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3585,19 +3924,19 @@
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
+        <v>43</v>
+      </c>
+      <c r="I64" t="s">
+        <v>44</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64" t="s">
         <v>37</v>
-      </c>
-      <c r="I64" t="s">
-        <v>38</v>
-      </c>
-      <c r="J64">
-        <v>4</v>
-      </c>
-      <c r="K64" t="s">
-        <v>33</v>
       </c>
       <c r="L64">
         <v>7</v>
@@ -3608,13 +3947,16 @@
       <c r="O64">
         <v>3</v>
       </c>
-      <c r="R64" t="s">
-        <v>30</v>
-      </c>
-      <c r="U64" t="s">
-        <v>30</v>
-      </c>
-      <c r="X64">
+      <c r="P64" t="s">
+        <v>61</v>
+      </c>
+      <c r="W64" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB64">
         <v>4</v>
       </c>
     </row>
@@ -3626,7 +3968,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3638,33 +3980,36 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J65">
         <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L65">
         <v>6</v>
       </c>
-      <c r="R65" t="s">
-        <v>36</v>
-      </c>
-      <c r="S65" t="s">
-        <v>40</v>
-      </c>
-      <c r="U65" t="s">
-        <v>36</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>50</v>
+      </c>
+      <c r="W65" t="s">
+        <v>42</v>
+      </c>
+      <c r="X65" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB65">
         <v>4</v>
       </c>
     </row>
@@ -3676,7 +4021,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3688,15 +4033,15 @@
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I66" t="s">
-        <v>70</v>
-      </c>
-      <c r="X66">
+        <v>86</v>
+      </c>
+      <c r="AB66">
         <v>4</v>
       </c>
     </row>
@@ -3708,7 +4053,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3720,15 +4065,15 @@
         <v>-40</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I67" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q67">
+        <v>94</v>
+      </c>
+      <c r="V67">
         <v>37</v>
       </c>
     </row>
@@ -3740,7 +4085,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3752,19 +4097,19 @@
         <v>-41</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H68" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I68" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L68">
         <v>7</v>
@@ -3775,19 +4120,25 @@
       <c r="O68">
         <v>9</v>
       </c>
-      <c r="R68" t="s">
-        <v>30</v>
-      </c>
-      <c r="S68" t="s">
-        <v>41</v>
-      </c>
-      <c r="U68" t="s">
-        <v>30</v>
-      </c>
-      <c r="W68">
-        <v>3</v>
-      </c>
-      <c r="X68">
+      <c r="P68" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>47</v>
+      </c>
+      <c r="S68">
+        <v>3</v>
+      </c>
+      <c r="W68" t="s">
+        <v>34</v>
+      </c>
+      <c r="X68" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3799,7 +4150,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3811,16 +4162,16 @@
         <v>-41</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H69" t="s">
+        <v>43</v>
+      </c>
+      <c r="I69" t="s">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s">
         <v>37</v>
-      </c>
-      <c r="I69" t="s">
-        <v>76</v>
-      </c>
-      <c r="K69" t="s">
-        <v>33</v>
       </c>
       <c r="L69">
         <v>6</v>
@@ -3831,19 +4182,25 @@
       <c r="O69">
         <v>8</v>
       </c>
-      <c r="R69" t="s">
-        <v>36</v>
-      </c>
-      <c r="S69" t="s">
-        <v>35</v>
-      </c>
-      <c r="U69" t="s">
-        <v>36</v>
-      </c>
-      <c r="W69">
-        <v>3</v>
-      </c>
-      <c r="X69">
+      <c r="P69" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>47</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="W69" t="s">
+        <v>42</v>
+      </c>
+      <c r="X69" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3855,7 +4212,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3867,33 +4224,36 @@
         <v>-40</v>
       </c>
       <c r="G70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L70">
         <v>7</v>
       </c>
-      <c r="R70" t="s">
-        <v>30</v>
-      </c>
-      <c r="S70" t="s">
-        <v>40</v>
-      </c>
-      <c r="U70" t="s">
-        <v>30</v>
-      </c>
-      <c r="X70">
+      <c r="P70" t="s">
+        <v>50</v>
+      </c>
+      <c r="W70" t="s">
+        <v>34</v>
+      </c>
+      <c r="X70" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3905,7 +4265,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -3917,19 +4277,19 @@
         <v>-40</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I71" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J71">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L71">
         <v>6</v>
@@ -3940,19 +4300,22 @@
       <c r="O71">
         <v>1</v>
       </c>
-      <c r="R71" t="s">
-        <v>36</v>
-      </c>
-      <c r="S71" t="s">
-        <v>62</v>
-      </c>
-      <c r="U71" t="s">
-        <v>36</v>
-      </c>
-      <c r="V71" t="s">
-        <v>36</v>
-      </c>
-      <c r="X71">
+      <c r="P71" t="s">
+        <v>61</v>
+      </c>
+      <c r="W71" t="s">
+        <v>42</v>
+      </c>
+      <c r="X71" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3964,7 +4327,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -3976,19 +4339,19 @@
         <v>-40</v>
       </c>
       <c r="G72" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H72" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I72" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L72">
         <v>7</v>
@@ -3999,13 +4362,16 @@
       <c r="O72">
         <v>9</v>
       </c>
-      <c r="R72" t="s">
-        <v>30</v>
-      </c>
-      <c r="S72" t="s">
-        <v>66</v>
-      </c>
-      <c r="X72">
+      <c r="P72" t="s">
+        <v>50</v>
+      </c>
+      <c r="W72" t="s">
+        <v>34</v>
+      </c>
+      <c r="X72" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB72">
         <v>5</v>
       </c>
     </row>
@@ -4017,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -4029,15 +4395,15 @@
         <v>-41</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H73" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I73" t="s">
-        <v>51</v>
-      </c>
-      <c r="X73">
+        <v>67</v>
+      </c>
+      <c r="AB73">
         <v>5</v>
       </c>
     </row>
@@ -4049,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -4061,36 +4427,42 @@
         <v>49</v>
       </c>
       <c r="G74" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H74" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I74" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="J74">
         <v>-5</v>
       </c>
       <c r="K74" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L74">
         <v>6</v>
       </c>
-      <c r="R74" t="s">
-        <v>30</v>
-      </c>
-      <c r="S74" t="s">
-        <v>66</v>
-      </c>
-      <c r="U74" t="s">
-        <v>30</v>
-      </c>
-      <c r="W74">
+      <c r="P74" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>53</v>
+      </c>
+      <c r="S74">
         <v>6</v>
       </c>
-      <c r="X74">
+      <c r="W74" t="s">
+        <v>34</v>
+      </c>
+      <c r="X74" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB74">
         <v>6</v>
       </c>
     </row>
@@ -4102,7 +4474,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -4114,36 +4486,39 @@
         <v>-44</v>
       </c>
       <c r="G75" t="s">
+        <v>42</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75" t="s">
         <v>36</v>
       </c>
-      <c r="H75" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" t="s">
-        <v>32</v>
-      </c>
       <c r="J75">
         <v>3</v>
       </c>
       <c r="K75" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
       <c r="M75" t="s">
-        <v>34</v>
-      </c>
-      <c r="U75" t="s">
-        <v>36</v>
-      </c>
-      <c r="V75" t="s">
-        <v>36</v>
-      </c>
-      <c r="W75">
+        <v>38</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>53</v>
+      </c>
+      <c r="S75">
         <v>6</v>
       </c>
-      <c r="X75">
+      <c r="Z75" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB75">
         <v>6</v>
       </c>
     </row>
@@ -4155,7 +4530,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -4167,18 +4542,18 @@
         <v>-40</v>
       </c>
       <c r="G76" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H76" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="I76" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q76">
+        <v>94</v>
+      </c>
+      <c r="V76">
         <v>23</v>
       </c>
-      <c r="X76">
+      <c r="AB76">
         <v>6</v>
       </c>
     </row>
@@ -4190,7 +4565,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4202,33 +4577,36 @@
         <v>-25</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J77">
         <v>6</v>
       </c>
       <c r="K77" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L77">
         <v>7</v>
       </c>
-      <c r="R77" t="s">
-        <v>36</v>
-      </c>
-      <c r="S77" t="s">
-        <v>40</v>
-      </c>
-      <c r="U77" t="s">
-        <v>36</v>
-      </c>
-      <c r="X77">
+      <c r="P77" t="s">
+        <v>50</v>
+      </c>
+      <c r="W77" t="s">
+        <v>42</v>
+      </c>
+      <c r="X77" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -4240,7 +4618,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4252,33 +4630,36 @@
         <v>-31</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J78">
         <v>-5</v>
       </c>
       <c r="K78" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N78">
         <v>7</v>
       </c>
-      <c r="R78" t="s">
-        <v>55</v>
-      </c>
-      <c r="S78" t="s">
-        <v>56</v>
-      </c>
-      <c r="U78" t="s">
-        <v>30</v>
-      </c>
-      <c r="X78">
+      <c r="P78" t="s">
+        <v>50</v>
+      </c>
+      <c r="W78" t="s">
+        <v>71</v>
+      </c>
+      <c r="X78" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -4290,7 +4671,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4302,27 +4683,30 @@
         <v>-26</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H79" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I79" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J79">
         <v>-5</v>
       </c>
       <c r="K79" t="s">
-        <v>39</v>
-      </c>
-      <c r="R79" t="s">
-        <v>30</v>
-      </c>
-      <c r="S79" t="s">
-        <v>60</v>
-      </c>
-      <c r="X79">
+        <v>45</v>
+      </c>
+      <c r="P79" t="s">
+        <v>50</v>
+      </c>
+      <c r="W79" t="s">
+        <v>34</v>
+      </c>
+      <c r="X79" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -4334,7 +4718,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -4346,30 +4730,33 @@
         <v>-21</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J80">
         <v>6</v>
       </c>
       <c r="K80" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L80">
         <v>8</v>
       </c>
-      <c r="R80" t="s">
-        <v>30</v>
-      </c>
-      <c r="U80" t="s">
-        <v>30</v>
-      </c>
-      <c r="X80">
+      <c r="P80" t="s">
+        <v>50</v>
+      </c>
+      <c r="W80" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB80">
         <v>5</v>
       </c>
     </row>
@@ -4381,7 +4768,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -4393,19 +4780,19 @@
         <v>-27</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H81" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I81" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L81">
         <v>6</v>
@@ -4416,16 +4803,19 @@
       <c r="O81">
         <v>9</v>
       </c>
-      <c r="R81" t="s">
-        <v>36</v>
-      </c>
-      <c r="S81" t="s">
-        <v>58</v>
-      </c>
-      <c r="U81" t="s">
-        <v>30</v>
-      </c>
-      <c r="X81">
+      <c r="P81" t="s">
+        <v>61</v>
+      </c>
+      <c r="W81" t="s">
+        <v>42</v>
+      </c>
+      <c r="X81" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB81">
         <v>5</v>
       </c>
     </row>
@@ -4437,7 +4827,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -4449,15 +4839,15 @@
         <v>-27</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I82" t="s">
-        <v>65</v>
-      </c>
-      <c r="X82">
+        <v>81</v>
+      </c>
+      <c r="AB82">
         <v>5</v>
       </c>
     </row>
@@ -4469,7 +4859,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4481,19 +4871,19 @@
         <v>-43</v>
       </c>
       <c r="G83" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I83" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J83">
         <v>12</v>
       </c>
       <c r="K83" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L83">
         <v>7</v>
@@ -4504,19 +4894,25 @@
       <c r="O83">
         <v>3</v>
       </c>
-      <c r="R83" t="s">
-        <v>30</v>
-      </c>
-      <c r="S83" t="s">
-        <v>60</v>
-      </c>
-      <c r="U83" t="s">
-        <v>30</v>
-      </c>
-      <c r="W83">
+      <c r="P83" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>47</v>
+      </c>
+      <c r="S83">
         <v>6</v>
       </c>
-      <c r="X83">
+      <c r="W83" t="s">
+        <v>34</v>
+      </c>
+      <c r="X83" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB83">
         <v>7</v>
       </c>
     </row>
@@ -4528,7 +4924,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4540,36 +4936,42 @@
         <v>45</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H84" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I84" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="J84">
         <v>6</v>
       </c>
       <c r="K84" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L84">
         <v>7</v>
       </c>
-      <c r="R84" t="s">
-        <v>36</v>
-      </c>
-      <c r="S84" t="s">
-        <v>41</v>
-      </c>
-      <c r="U84" t="s">
-        <v>30</v>
-      </c>
-      <c r="W84">
+      <c r="P84" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>47</v>
+      </c>
+      <c r="S84">
         <v>6</v>
       </c>
-      <c r="X84">
+      <c r="W84" t="s">
+        <v>42</v>
+      </c>
+      <c r="X84" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB84">
         <v>7</v>
       </c>
     </row>
@@ -4581,7 +4983,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4593,19 +4995,19 @@
         <v>39</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I85" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J85">
         <v>10</v>
       </c>
       <c r="K85" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L85">
         <v>6</v>
@@ -4616,19 +5018,28 @@
       <c r="O85">
         <v>5</v>
       </c>
+      <c r="P85" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>47</v>
+      </c>
       <c r="R85" t="s">
-        <v>36</v>
-      </c>
-      <c r="S85" t="s">
-        <v>40</v>
-      </c>
-      <c r="U85" t="s">
-        <v>36</v>
-      </c>
-      <c r="W85">
+        <v>97</v>
+      </c>
+      <c r="S85">
         <v>6</v>
       </c>
-      <c r="X85">
+      <c r="W85" t="s">
+        <v>42</v>
+      </c>
+      <c r="X85" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB85">
         <v>7</v>
       </c>
     </row>
@@ -4640,7 +5051,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4652,39 +5063,45 @@
         <v>29</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J86">
         <v>12</v>
       </c>
       <c r="K86" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L86">
         <v>7</v>
       </c>
       <c r="M86" t="s">
-        <v>73</v>
-      </c>
-      <c r="R86" t="s">
-        <v>36</v>
-      </c>
-      <c r="S86" t="s">
-        <v>40</v>
-      </c>
-      <c r="U86" t="s">
-        <v>30</v>
-      </c>
-      <c r="W86">
+        <v>91</v>
+      </c>
+      <c r="P86" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>47</v>
+      </c>
+      <c r="S86">
         <v>6</v>
       </c>
-      <c r="X86">
+      <c r="W86" t="s">
+        <v>42</v>
+      </c>
+      <c r="X86" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB86">
         <v>7</v>
       </c>
     </row>
@@ -4696,7 +5113,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4708,39 +5125,45 @@
         <v>17</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H87" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J87">
         <v>11</v>
       </c>
       <c r="K87" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L87">
         <v>9</v>
       </c>
       <c r="M87" t="s">
-        <v>43</v>
-      </c>
-      <c r="R87" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="P87" t="s">
+        <v>46</v>
       </c>
       <c r="S87" t="s">
-        <v>78</v>
-      </c>
-      <c r="U87" t="s">
-        <v>30</v>
+        <v>98</v>
+      </c>
+      <c r="T87" t="s">
+        <v>99</v>
       </c>
       <c r="W87" t="s">
-        <v>79</v>
-      </c>
-      <c r="X87">
+        <v>42</v>
+      </c>
+      <c r="X87" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB87">
         <v>7</v>
       </c>
     </row>
@@ -4752,7 +5175,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4764,19 +5187,19 @@
         <v>6</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H88" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I88" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J88">
         <v>5</v>
       </c>
       <c r="K88" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L88">
         <v>8</v>
@@ -4787,19 +5210,28 @@
       <c r="O88">
         <v>3</v>
       </c>
+      <c r="P88" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>101</v>
+      </c>
       <c r="R88" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" t="s">
-        <v>35</v>
-      </c>
-      <c r="U88" t="s">
-        <v>30</v>
-      </c>
-      <c r="W88">
-        <v>3</v>
-      </c>
-      <c r="X88">
+        <v>102</v>
+      </c>
+      <c r="S88">
+        <v>3</v>
+      </c>
+      <c r="W88" t="s">
+        <v>34</v>
+      </c>
+      <c r="X88" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB88">
         <v>7</v>
       </c>
     </row>
@@ -4811,7 +5243,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4823,36 +5255,42 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L89">
         <v>8</v>
       </c>
       <c r="M89" t="s">
-        <v>80</v>
-      </c>
-      <c r="R89" t="s">
-        <v>36</v>
-      </c>
-      <c r="S89" t="s">
-        <v>35</v>
-      </c>
-      <c r="U89" t="s">
-        <v>36</v>
-      </c>
-      <c r="X89">
+        <v>103</v>
+      </c>
+      <c r="P89" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>101</v>
+      </c>
+      <c r="W89" t="s">
+        <v>42</v>
+      </c>
+      <c r="X89" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB89">
         <v>7</v>
       </c>
     </row>
@@ -4864,7 +5302,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4876,19 +5314,19 @@
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H90" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I90" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="J90">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L90">
         <v>9</v>
@@ -4899,19 +5337,28 @@
       <c r="O90">
         <v>2</v>
       </c>
-      <c r="R90" t="s">
-        <v>36</v>
+      <c r="P90" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>47</v>
       </c>
       <c r="S90" t="s">
-        <v>35</v>
-      </c>
-      <c r="U90" t="s">
-        <v>36</v>
+        <v>98</v>
+      </c>
+      <c r="T90" t="s">
+        <v>99</v>
       </c>
       <c r="W90" t="s">
-        <v>79</v>
-      </c>
-      <c r="X90">
+        <v>42</v>
+      </c>
+      <c r="X90" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB90">
         <v>7</v>
       </c>
     </row>
@@ -4923,7 +5370,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4935,15 +5382,15 @@
         <v>3</v>
       </c>
       <c r="G91" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H91" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="I91" t="s">
-        <v>47</v>
-      </c>
-      <c r="X91">
+        <v>63</v>
+      </c>
+      <c r="AB91">
         <v>7</v>
       </c>
     </row>
@@ -4955,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4967,15 +5414,15 @@
         <v>2</v>
       </c>
       <c r="G92" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="I92" t="s">
-        <v>70</v>
-      </c>
-      <c r="X92">
+        <v>86</v>
+      </c>
+      <c r="AB92">
         <v>7</v>
       </c>
     </row>
@@ -4987,7 +5434,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4999,15 +5446,15 @@
         <v>-40</v>
       </c>
       <c r="G93" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H93" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="I93" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q93">
+        <v>94</v>
+      </c>
+      <c r="V93">
         <v>20</v>
       </c>
     </row>
@@ -5019,7 +5466,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5031,33 +5478,36 @@
         <v>-25</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I94" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L94">
         <v>7</v>
       </c>
-      <c r="R94" t="s">
-        <v>30</v>
-      </c>
-      <c r="S94" t="s">
-        <v>40</v>
-      </c>
-      <c r="U94" t="s">
-        <v>30</v>
-      </c>
-      <c r="X94">
+      <c r="P94" t="s">
+        <v>50</v>
+      </c>
+      <c r="W94" t="s">
+        <v>34</v>
+      </c>
+      <c r="X94" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB94">
         <v>6</v>
       </c>
     </row>
@@ -5069,7 +5519,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -5081,19 +5531,19 @@
         <v>-25</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H95" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I95" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J95">
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L95">
         <v>7</v>
@@ -5104,16 +5554,19 @@
       <c r="O95">
         <v>5</v>
       </c>
-      <c r="R95" t="s">
-        <v>55</v>
-      </c>
-      <c r="S95" t="s">
-        <v>56</v>
-      </c>
-      <c r="U95" t="s">
-        <v>30</v>
-      </c>
-      <c r="X95">
+      <c r="P95" t="s">
+        <v>50</v>
+      </c>
+      <c r="W95" t="s">
+        <v>71</v>
+      </c>
+      <c r="X95" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB95">
         <v>6</v>
       </c>
     </row>
@@ -5125,7 +5578,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5137,33 +5590,36 @@
         <v>-40</v>
       </c>
       <c r="G96" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J96">
         <v>26</v>
       </c>
       <c r="K96" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L96">
         <v>8</v>
       </c>
-      <c r="R96" t="s">
-        <v>36</v>
-      </c>
-      <c r="S96" t="s">
-        <v>40</v>
-      </c>
-      <c r="U96" t="s">
-        <v>36</v>
-      </c>
-      <c r="X96">
+      <c r="P96" t="s">
+        <v>50</v>
+      </c>
+      <c r="W96" t="s">
+        <v>42</v>
+      </c>
+      <c r="X96" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB96">
         <v>6</v>
       </c>
     </row>
@@ -5175,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -5187,33 +5643,36 @@
         <v>34</v>
       </c>
       <c r="G97" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>9</v>
       </c>
       <c r="K97" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L97">
         <v>8</v>
       </c>
-      <c r="R97" t="s">
-        <v>36</v>
-      </c>
-      <c r="S97" t="s">
-        <v>40</v>
-      </c>
-      <c r="U97" t="s">
-        <v>36</v>
-      </c>
-      <c r="X97">
+      <c r="P97" t="s">
+        <v>50</v>
+      </c>
+      <c r="W97" t="s">
+        <v>42</v>
+      </c>
+      <c r="X97" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB97">
         <v>6</v>
       </c>
     </row>
@@ -5225,7 +5684,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5237,33 +5696,36 @@
         <v>25</v>
       </c>
       <c r="G98" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J98">
         <v>-1</v>
       </c>
       <c r="K98" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L98">
         <v>7</v>
       </c>
-      <c r="R98" t="s">
-        <v>36</v>
-      </c>
-      <c r="S98" t="s">
-        <v>40</v>
-      </c>
-      <c r="U98" t="s">
-        <v>30</v>
-      </c>
-      <c r="X98">
+      <c r="P98" t="s">
+        <v>50</v>
+      </c>
+      <c r="W98" t="s">
+        <v>42</v>
+      </c>
+      <c r="X98" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB98">
         <v>6</v>
       </c>
     </row>
@@ -5275,7 +5737,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -5287,33 +5749,36 @@
         <v>26</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J99">
         <v>5</v>
       </c>
       <c r="K99" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L99">
         <v>7</v>
       </c>
-      <c r="R99" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" t="s">
-        <v>64</v>
-      </c>
-      <c r="U99" t="s">
-        <v>30</v>
-      </c>
-      <c r="X99">
+      <c r="P99" t="s">
+        <v>50</v>
+      </c>
+      <c r="W99" t="s">
+        <v>34</v>
+      </c>
+      <c r="X99" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB99">
         <v>6</v>
       </c>
     </row>
@@ -5325,7 +5790,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -5337,33 +5802,36 @@
         <v>21</v>
       </c>
       <c r="G100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J100">
         <v>12</v>
       </c>
       <c r="K100" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L100">
         <v>7</v>
       </c>
-      <c r="R100" t="s">
-        <v>30</v>
-      </c>
-      <c r="S100" t="s">
-        <v>64</v>
-      </c>
-      <c r="U100" t="s">
-        <v>30</v>
-      </c>
-      <c r="X100">
+      <c r="P100" t="s">
+        <v>50</v>
+      </c>
+      <c r="W100" t="s">
+        <v>34</v>
+      </c>
+      <c r="X100" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB100">
         <v>6</v>
       </c>
     </row>
@@ -5375,7 +5843,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -5387,33 +5855,36 @@
         <v>9</v>
       </c>
       <c r="G101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J101">
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L101">
         <v>8</v>
       </c>
-      <c r="R101" t="s">
-        <v>30</v>
-      </c>
-      <c r="S101" t="s">
-        <v>64</v>
-      </c>
-      <c r="U101" t="s">
-        <v>30</v>
-      </c>
-      <c r="X101">
+      <c r="P101" t="s">
+        <v>50</v>
+      </c>
+      <c r="W101" t="s">
+        <v>34</v>
+      </c>
+      <c r="X101" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB101">
         <v>6</v>
       </c>
     </row>
@@ -5425,7 +5896,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5437,33 +5908,36 @@
         <v>6</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J102">
         <v>6</v>
       </c>
       <c r="K102" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L102">
         <v>10</v>
       </c>
-      <c r="R102" t="s">
-        <v>55</v>
-      </c>
-      <c r="S102" t="s">
-        <v>74</v>
-      </c>
-      <c r="U102" t="s">
-        <v>30</v>
-      </c>
-      <c r="X102">
+      <c r="P102" t="s">
+        <v>50</v>
+      </c>
+      <c r="W102" t="s">
+        <v>71</v>
+      </c>
+      <c r="X102" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102">
         <v>6</v>
       </c>
     </row>
@@ -5475,7 +5949,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -5487,15 +5961,15 @@
         <v>3</v>
       </c>
       <c r="G103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I103" t="s">
-        <v>83</v>
-      </c>
-      <c r="X103">
+        <v>106</v>
+      </c>
+      <c r="AB103">
         <v>6</v>
       </c>
     </row>
@@ -5507,7 +5981,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -5519,15 +5993,15 @@
         <v>3</v>
       </c>
       <c r="G104" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H104" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I104" t="s">
-        <v>70</v>
-      </c>
-      <c r="X104">
+        <v>86</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -5539,7 +6013,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -5551,13 +6025,13 @@
         <v>-40</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I105" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106">
@@ -5568,7 +6042,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5580,24 +6054,27 @@
         <v>-20</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I106" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J106">
         <v>-5</v>
       </c>
       <c r="K106" t="s">
-        <v>33</v>
-      </c>
-      <c r="W106">
+        <v>37</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>47</v>
+      </c>
+      <c r="S106">
         <v>6</v>
       </c>
-      <c r="X106">
+      <c r="AB106">
         <v>7</v>
       </c>
     </row>
@@ -5609,7 +6086,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -5621,39 +6098,45 @@
         <v>-15</v>
       </c>
       <c r="G107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L107">
         <v>7</v>
       </c>
       <c r="M107" t="s">
-        <v>80</v>
-      </c>
-      <c r="R107" t="s">
-        <v>36</v>
-      </c>
-      <c r="S107" t="s">
-        <v>41</v>
-      </c>
-      <c r="U107" t="s">
-        <v>30</v>
-      </c>
-      <c r="W107">
+        <v>103</v>
+      </c>
+      <c r="P107" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>47</v>
+      </c>
+      <c r="S107">
         <v>6</v>
       </c>
-      <c r="X107">
+      <c r="W107" t="s">
+        <v>42</v>
+      </c>
+      <c r="X107" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB107">
         <v>7</v>
       </c>
     </row>
@@ -5665,7 +6148,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -5677,19 +6160,19 @@
         <v>-15</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I108" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L108">
         <v>6</v>
@@ -5700,19 +6183,28 @@
       <c r="O108">
         <v>3</v>
       </c>
+      <c r="P108" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>47</v>
+      </c>
       <c r="R108" t="s">
-        <v>30</v>
-      </c>
-      <c r="S108" t="s">
-        <v>41</v>
-      </c>
-      <c r="U108" t="s">
-        <v>30</v>
-      </c>
-      <c r="W108">
+        <v>97</v>
+      </c>
+      <c r="S108">
         <v>6</v>
       </c>
-      <c r="X108">
+      <c r="W108" t="s">
+        <v>34</v>
+      </c>
+      <c r="X108" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB108">
         <v>7</v>
       </c>
     </row>
@@ -5724,7 +6216,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -5736,30 +6228,33 @@
         <v>-15</v>
       </c>
       <c r="G109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I109" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="J109">
         <v>-9</v>
       </c>
       <c r="K109" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L109">
         <v>6</v>
       </c>
-      <c r="U109" t="s">
-        <v>36</v>
-      </c>
-      <c r="W109" t="s">
-        <v>49</v>
-      </c>
-      <c r="X109">
+      <c r="Q109" t="s">
+        <v>53</v>
+      </c>
+      <c r="S109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB109">
         <v>7</v>
       </c>
     </row>
@@ -5771,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5783,15 +6278,15 @@
         <v>-6</v>
       </c>
       <c r="G110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H110" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I110" t="s">
-        <v>84</v>
-      </c>
-      <c r="X110">
+        <v>107</v>
+      </c>
+      <c r="AB110">
         <v>7</v>
       </c>
     </row>
@@ -5803,7 +6298,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5815,33 +6310,36 @@
         <v>32</v>
       </c>
       <c r="G111" t="s">
+        <v>42</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111" t="s">
         <v>36</v>
       </c>
-      <c r="H111" t="s">
-        <v>31</v>
-      </c>
-      <c r="I111" t="s">
-        <v>32</v>
-      </c>
       <c r="J111">
         <v>4</v>
       </c>
       <c r="K111" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L111">
         <v>7</v>
       </c>
-      <c r="R111" t="s">
-        <v>30</v>
-      </c>
-      <c r="S111" t="s">
-        <v>40</v>
-      </c>
-      <c r="U111" t="s">
-        <v>36</v>
-      </c>
-      <c r="X111">
+      <c r="P111" t="s">
+        <v>50</v>
+      </c>
+      <c r="W111" t="s">
+        <v>34</v>
+      </c>
+      <c r="X111" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB111">
         <v>9</v>
       </c>
     </row>
@@ -5853,7 +6351,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -5865,33 +6363,36 @@
         <v>28</v>
       </c>
       <c r="G112" t="s">
+        <v>42</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" t="s">
         <v>36</v>
-      </c>
-      <c r="H112" t="s">
-        <v>31</v>
-      </c>
-      <c r="I112" t="s">
-        <v>32</v>
       </c>
       <c r="J112">
         <v>8</v>
       </c>
       <c r="K112" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L112">
         <v>7</v>
       </c>
-      <c r="R112" t="s">
-        <v>30</v>
-      </c>
-      <c r="S112" t="s">
-        <v>64</v>
-      </c>
-      <c r="U112" t="s">
-        <v>30</v>
-      </c>
-      <c r="X112">
+      <c r="P112" t="s">
+        <v>50</v>
+      </c>
+      <c r="W112" t="s">
+        <v>34</v>
+      </c>
+      <c r="X112" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB112">
         <v>9</v>
       </c>
     </row>
@@ -5903,7 +6404,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -5915,33 +6416,36 @@
         <v>20</v>
       </c>
       <c r="G113" t="s">
+        <v>42</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113" t="s">
         <v>36</v>
       </c>
-      <c r="H113" t="s">
-        <v>31</v>
-      </c>
-      <c r="I113" t="s">
-        <v>32</v>
-      </c>
       <c r="J113">
         <v>4</v>
       </c>
       <c r="K113" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L113">
         <v>7</v>
       </c>
-      <c r="R113" t="s">
-        <v>30</v>
-      </c>
-      <c r="S113" t="s">
-        <v>64</v>
-      </c>
-      <c r="U113" t="s">
-        <v>36</v>
-      </c>
-      <c r="X113">
+      <c r="P113" t="s">
+        <v>50</v>
+      </c>
+      <c r="W113" t="s">
+        <v>34</v>
+      </c>
+      <c r="X113" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB113">
         <v>9</v>
       </c>
     </row>
@@ -5953,7 +6457,7 @@
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -5965,33 +6469,36 @@
         <v>16</v>
       </c>
       <c r="G114" t="s">
+        <v>42</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114" t="s">
         <v>36</v>
       </c>
-      <c r="H114" t="s">
-        <v>31</v>
-      </c>
-      <c r="I114" t="s">
-        <v>32</v>
-      </c>
       <c r="J114">
         <v>3</v>
       </c>
       <c r="K114" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L114">
         <v>7</v>
       </c>
-      <c r="R114" t="s">
-        <v>30</v>
-      </c>
-      <c r="S114" t="s">
-        <v>64</v>
-      </c>
-      <c r="U114" t="s">
-        <v>30</v>
-      </c>
-      <c r="X114">
+      <c r="P114" t="s">
+        <v>50</v>
+      </c>
+      <c r="W114" t="s">
+        <v>34</v>
+      </c>
+      <c r="X114" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB114">
         <v>9</v>
       </c>
     </row>
@@ -6003,7 +6510,7 @@
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -6015,33 +6522,36 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H115" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I115" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J115">
         <v>-2</v>
       </c>
       <c r="K115" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L115">
         <v>9</v>
       </c>
-      <c r="R115" t="s">
-        <v>55</v>
-      </c>
-      <c r="S115" t="s">
-        <v>74</v>
-      </c>
-      <c r="U115" t="s">
-        <v>36</v>
-      </c>
-      <c r="X115">
+      <c r="P115" t="s">
+        <v>50</v>
+      </c>
+      <c r="W115" t="s">
+        <v>71</v>
+      </c>
+      <c r="X115" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB115">
         <v>9</v>
       </c>
     </row>
@@ -6053,7 +6563,7 @@
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -6065,15 +6575,15 @@
         <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H116" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="I116" t="s">
-        <v>70</v>
-      </c>
-      <c r="X116">
+        <v>86</v>
+      </c>
+      <c r="AB116">
         <v>9</v>
       </c>
     </row>
@@ -6085,7 +6595,7 @@
         <v>3</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -6097,15 +6607,15 @@
         <v>-40</v>
       </c>
       <c r="G117" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H117" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I117" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q117">
+        <v>94</v>
+      </c>
+      <c r="V117">
         <v>10</v>
       </c>
     </row>
@@ -6117,7 +6627,7 @@
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -6129,39 +6639,45 @@
         <v>-15</v>
       </c>
       <c r="G118" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H118" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I118" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L118">
         <v>7</v>
       </c>
       <c r="M118" t="s">
-        <v>34</v>
-      </c>
-      <c r="R118" t="s">
-        <v>36</v>
-      </c>
-      <c r="S118" t="s">
-        <v>41</v>
-      </c>
-      <c r="U118" t="s">
-        <v>30</v>
-      </c>
-      <c r="W118">
+        <v>38</v>
+      </c>
+      <c r="P118" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>47</v>
+      </c>
+      <c r="S118">
         <v>6</v>
       </c>
-      <c r="X118">
+      <c r="W118" t="s">
+        <v>42</v>
+      </c>
+      <c r="X118" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB118">
         <v>8</v>
       </c>
     </row>
@@ -6173,7 +6689,7 @@
         <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -6185,19 +6701,19 @@
         <v>-15</v>
       </c>
       <c r="G119" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I119" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L119">
         <v>6</v>
@@ -6208,19 +6724,25 @@
       <c r="O119">
         <v>3</v>
       </c>
-      <c r="R119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S119" t="s">
-        <v>41</v>
-      </c>
-      <c r="U119" t="s">
-        <v>30</v>
-      </c>
-      <c r="W119">
+      <c r="P119" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>47</v>
+      </c>
+      <c r="S119">
         <v>6</v>
       </c>
-      <c r="X119">
+      <c r="W119" t="s">
+        <v>34</v>
+      </c>
+      <c r="X119" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB119">
         <v>8</v>
       </c>
     </row>
@@ -6232,7 +6754,7 @@
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -6244,19 +6766,19 @@
         <v>-15</v>
       </c>
       <c r="G120" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H120" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I120" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J120">
         <v>45</v>
       </c>
       <c r="K120" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N120">
         <v>27</v>
@@ -6264,19 +6786,28 @@
       <c r="O120">
         <v>9</v>
       </c>
+      <c r="P120" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>47</v>
+      </c>
       <c r="R120" t="s">
-        <v>55</v>
-      </c>
-      <c r="S120" t="s">
-        <v>86</v>
-      </c>
-      <c r="U120" t="s">
-        <v>30</v>
-      </c>
-      <c r="W120">
+        <v>97</v>
+      </c>
+      <c r="S120">
         <v>6</v>
       </c>
-      <c r="X120">
+      <c r="W120" t="s">
+        <v>71</v>
+      </c>
+      <c r="X120" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB120">
         <v>8</v>
       </c>
     </row>
@@ -6288,7 +6819,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6300,33 +6831,36 @@
         <v>40</v>
       </c>
       <c r="G121" t="s">
+        <v>42</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121" t="s">
         <v>36</v>
-      </c>
-      <c r="H121" t="s">
-        <v>31</v>
-      </c>
-      <c r="I121" t="s">
-        <v>32</v>
       </c>
       <c r="J121">
         <v>8</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L121">
         <v>7</v>
       </c>
-      <c r="R121" t="s">
-        <v>30</v>
-      </c>
-      <c r="S121" t="s">
-        <v>40</v>
-      </c>
-      <c r="U121" t="s">
-        <v>36</v>
-      </c>
-      <c r="X121">
+      <c r="P121" t="s">
+        <v>50</v>
+      </c>
+      <c r="W121" t="s">
+        <v>34</v>
+      </c>
+      <c r="X121" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB121">
         <v>8</v>
       </c>
     </row>
@@ -6338,7 +6872,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6350,33 +6884,36 @@
         <v>32</v>
       </c>
       <c r="G122" t="s">
+        <v>42</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122" t="s">
         <v>36</v>
-      </c>
-      <c r="H122" t="s">
-        <v>31</v>
-      </c>
-      <c r="I122" t="s">
-        <v>32</v>
       </c>
       <c r="J122">
         <v>6</v>
       </c>
       <c r="K122" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L122">
         <v>8</v>
       </c>
-      <c r="R122" t="s">
-        <v>30</v>
-      </c>
-      <c r="S122" t="s">
-        <v>64</v>
-      </c>
-      <c r="U122" t="s">
-        <v>30</v>
-      </c>
-      <c r="X122">
+      <c r="P122" t="s">
+        <v>50</v>
+      </c>
+      <c r="W122" t="s">
+        <v>34</v>
+      </c>
+      <c r="X122" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB122">
         <v>8</v>
       </c>
     </row>
@@ -6388,7 +6925,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -6400,33 +6937,36 @@
         <v>26</v>
       </c>
       <c r="G123" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I123" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J123">
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L123">
         <v>7</v>
       </c>
-      <c r="R123" t="s">
-        <v>36</v>
-      </c>
-      <c r="S123" t="s">
-        <v>71</v>
-      </c>
-      <c r="U123" t="s">
-        <v>30</v>
-      </c>
-      <c r="X123">
+      <c r="P123" t="s">
+        <v>50</v>
+      </c>
+      <c r="W123" t="s">
+        <v>42</v>
+      </c>
+      <c r="X123" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB123">
         <v>8</v>
       </c>
     </row>
@@ -6438,7 +6978,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -6450,19 +6990,19 @@
         <v>24</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H124" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I124" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L124">
         <v>7</v>
@@ -6473,16 +7013,19 @@
       <c r="O124">
         <v>5</v>
       </c>
-      <c r="R124" t="s">
-        <v>36</v>
-      </c>
-      <c r="S124" t="s">
-        <v>66</v>
-      </c>
-      <c r="U124" t="s">
-        <v>36</v>
-      </c>
-      <c r="X124">
+      <c r="P124" t="s">
+        <v>61</v>
+      </c>
+      <c r="W124" t="s">
+        <v>42</v>
+      </c>
+      <c r="X124" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB124">
         <v>8</v>
       </c>
     </row>
@@ -6494,7 +7037,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D125">
         <v>3</v>
@@ -6506,33 +7049,36 @@
         <v>24</v>
       </c>
       <c r="G125" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I125" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J125">
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L125">
         <v>7</v>
       </c>
-      <c r="R125" t="s">
-        <v>36</v>
-      </c>
-      <c r="S125" t="s">
-        <v>40</v>
-      </c>
-      <c r="U125" t="s">
-        <v>30</v>
-      </c>
-      <c r="X125">
+      <c r="P125" t="s">
+        <v>50</v>
+      </c>
+      <c r="W125" t="s">
+        <v>42</v>
+      </c>
+      <c r="X125" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB125">
         <v>8</v>
       </c>
     </row>
@@ -6544,7 +7090,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -6556,15 +7102,15 @@
         <v>23</v>
       </c>
       <c r="G126" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H126" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="I126" t="s">
-        <v>70</v>
-      </c>
-      <c r="X126">
+        <v>86</v>
+      </c>
+      <c r="AB126">
         <v>8</v>
       </c>
     </row>
@@ -6576,7 +7122,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6588,13 +7134,13 @@
         <v>-40</v>
       </c>
       <c r="G127" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H127" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I127" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
@@ -6605,7 +7151,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -6617,39 +7163,45 @@
         <v>-20</v>
       </c>
       <c r="G128" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I128" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J128">
         <v>6</v>
       </c>
       <c r="K128" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L128">
         <v>6</v>
       </c>
       <c r="M128" t="s">
-        <v>73</v>
-      </c>
-      <c r="R128" t="s">
-        <v>30</v>
-      </c>
-      <c r="S128" t="s">
-        <v>72</v>
-      </c>
-      <c r="U128" t="s">
-        <v>36</v>
-      </c>
-      <c r="W128">
+        <v>91</v>
+      </c>
+      <c r="P128" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>47</v>
+      </c>
+      <c r="S128">
         <v>6</v>
       </c>
-      <c r="X128">
+      <c r="W128" t="s">
+        <v>34</v>
+      </c>
+      <c r="X128" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB128">
         <v>10</v>
       </c>
     </row>
@@ -6661,7 +7213,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -6673,39 +7225,45 @@
         <v>-26</v>
       </c>
       <c r="G129" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129" t="s">
         <v>36</v>
       </c>
-      <c r="H129" t="s">
-        <v>31</v>
-      </c>
-      <c r="I129" t="s">
-        <v>32</v>
-      </c>
       <c r="J129">
         <v>1</v>
       </c>
       <c r="K129" t="s">
+        <v>37</v>
+      </c>
+      <c r="L129">
+        <v>7</v>
+      </c>
+      <c r="M129" t="s">
         <v>33</v>
       </c>
-      <c r="L129">
-        <v>7</v>
-      </c>
-      <c r="M129" t="s">
-        <v>29</v>
-      </c>
-      <c r="R129" t="s">
-        <v>36</v>
-      </c>
-      <c r="S129" t="s">
-        <v>35</v>
-      </c>
-      <c r="U129" t="s">
-        <v>30</v>
-      </c>
-      <c r="W129">
+      <c r="P129" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>40</v>
+      </c>
+      <c r="S129">
         <v>6</v>
       </c>
-      <c r="X129">
+      <c r="W129" t="s">
+        <v>42</v>
+      </c>
+      <c r="X129" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB129">
         <v>10</v>
       </c>
     </row>
@@ -6717,7 +7275,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D130">
         <v>3</v>
@@ -6729,39 +7287,48 @@
         <v>-27</v>
       </c>
       <c r="G130" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J130">
         <v>-7</v>
       </c>
       <c r="K130" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L130">
         <v>6</v>
       </c>
       <c r="M130" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="P130" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>47</v>
       </c>
       <c r="R130" t="s">
-        <v>36</v>
-      </c>
-      <c r="S130" t="s">
-        <v>35</v>
-      </c>
-      <c r="U130" t="s">
-        <v>30</v>
-      </c>
-      <c r="W130">
+        <v>58</v>
+      </c>
+      <c r="S130">
         <v>6</v>
       </c>
-      <c r="X130">
+      <c r="W130" t="s">
+        <v>42</v>
+      </c>
+      <c r="X130" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB130">
         <v>10</v>
       </c>
     </row>
@@ -6773,7 +7340,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D131">
         <v>4</v>
@@ -6785,15 +7352,15 @@
         <v>-20</v>
       </c>
       <c r="G131" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H131" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I131" t="s">
-        <v>47</v>
-      </c>
-      <c r="X131">
+        <v>63</v>
+      </c>
+      <c r="AB131">
         <v>10</v>
       </c>
     </row>
@@ -6805,7 +7372,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D132">
         <v>4</v>
@@ -6817,15 +7384,15 @@
         <v>-15</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H132" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I132" t="s">
-        <v>51</v>
-      </c>
-      <c r="X132">
+        <v>67</v>
+      </c>
+      <c r="AB132">
         <v>10</v>
       </c>
     </row>
@@ -6837,7 +7404,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6849,33 +7416,36 @@
         <v>48</v>
       </c>
       <c r="G133" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J133">
         <v>10</v>
       </c>
       <c r="K133" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L133">
         <v>7</v>
       </c>
-      <c r="R133" t="s">
-        <v>36</v>
-      </c>
-      <c r="S133" t="s">
-        <v>40</v>
-      </c>
-      <c r="U133" t="s">
-        <v>30</v>
-      </c>
-      <c r="X133">
+      <c r="P133" t="s">
+        <v>50</v>
+      </c>
+      <c r="W133" t="s">
+        <v>42</v>
+      </c>
+      <c r="X133" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB133">
         <v>9</v>
       </c>
     </row>
@@ -6887,7 +7457,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -6899,27 +7469,30 @@
         <v>38</v>
       </c>
       <c r="G134" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H134" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I134" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J134">
         <v>-5</v>
       </c>
       <c r="K134" t="s">
-        <v>39</v>
-      </c>
-      <c r="R134" t="s">
-        <v>36</v>
-      </c>
-      <c r="S134" t="s">
-        <v>72</v>
-      </c>
-      <c r="X134">
+        <v>45</v>
+      </c>
+      <c r="P134" t="s">
+        <v>88</v>
+      </c>
+      <c r="W134" t="s">
+        <v>42</v>
+      </c>
+      <c r="X134" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB134">
         <v>9</v>
       </c>
     </row>
@@ -6931,7 +7504,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -6943,33 +7516,36 @@
         <v>43</v>
       </c>
       <c r="G135" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H135" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I135" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J135">
         <v>13</v>
       </c>
       <c r="K135" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L135">
         <v>7</v>
       </c>
-      <c r="R135" t="s">
-        <v>36</v>
-      </c>
-      <c r="S135" t="s">
-        <v>72</v>
-      </c>
-      <c r="U135" t="s">
-        <v>36</v>
-      </c>
-      <c r="X135">
+      <c r="P135" t="s">
+        <v>88</v>
+      </c>
+      <c r="W135" t="s">
+        <v>42</v>
+      </c>
+      <c r="X135" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB135">
         <v>9</v>
       </c>
     </row>
@@ -6981,7 +7557,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -6993,33 +7569,36 @@
         <v>30</v>
       </c>
       <c r="G136" t="s">
+        <v>42</v>
+      </c>
+      <c r="H136" t="s">
+        <v>35</v>
+      </c>
+      <c r="I136" t="s">
         <v>36</v>
-      </c>
-      <c r="H136" t="s">
-        <v>31</v>
-      </c>
-      <c r="I136" t="s">
-        <v>32</v>
       </c>
       <c r="J136">
         <v>13</v>
       </c>
       <c r="K136" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L136">
         <v>8</v>
       </c>
-      <c r="R136" t="s">
-        <v>36</v>
-      </c>
-      <c r="S136" t="s">
-        <v>72</v>
-      </c>
-      <c r="U136" t="s">
-        <v>36</v>
-      </c>
-      <c r="X136">
+      <c r="P136" t="s">
+        <v>88</v>
+      </c>
+      <c r="W136" t="s">
+        <v>42</v>
+      </c>
+      <c r="X136" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB136">
         <v>9</v>
       </c>
     </row>
@@ -7031,7 +7610,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -7043,33 +7622,36 @@
         <v>17</v>
       </c>
       <c r="G137" t="s">
+        <v>42</v>
+      </c>
+      <c r="H137" t="s">
+        <v>35</v>
+      </c>
+      <c r="I137" t="s">
         <v>36</v>
-      </c>
-      <c r="H137" t="s">
-        <v>31</v>
-      </c>
-      <c r="I137" t="s">
-        <v>32</v>
       </c>
       <c r="J137">
         <v>9</v>
       </c>
       <c r="K137" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L137">
         <v>8</v>
       </c>
-      <c r="R137" t="s">
-        <v>30</v>
-      </c>
-      <c r="S137" t="s">
-        <v>87</v>
-      </c>
-      <c r="U137" t="s">
-        <v>30</v>
-      </c>
-      <c r="X137">
+      <c r="P137" t="s">
+        <v>88</v>
+      </c>
+      <c r="W137" t="s">
+        <v>34</v>
+      </c>
+      <c r="X137" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB137">
         <v>9</v>
       </c>
     </row>
@@ -7081,7 +7663,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -7093,33 +7675,36 @@
         <v>8</v>
       </c>
       <c r="G138" t="s">
+        <v>42</v>
+      </c>
+      <c r="H138" t="s">
+        <v>35</v>
+      </c>
+      <c r="I138" t="s">
         <v>36</v>
       </c>
-      <c r="H138" t="s">
-        <v>31</v>
-      </c>
-      <c r="I138" t="s">
-        <v>32</v>
-      </c>
       <c r="J138">
         <v>4</v>
       </c>
       <c r="K138" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L138">
         <v>8</v>
       </c>
-      <c r="R138" t="s">
-        <v>30</v>
-      </c>
-      <c r="S138" t="s">
-        <v>88</v>
-      </c>
-      <c r="U138" t="s">
-        <v>30</v>
-      </c>
-      <c r="X138">
+      <c r="P138" t="s">
+        <v>50</v>
+      </c>
+      <c r="W138" t="s">
+        <v>34</v>
+      </c>
+      <c r="X138" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB138">
         <v>9</v>
       </c>
     </row>
@@ -7131,7 +7716,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -7143,33 +7728,36 @@
         <v>4</v>
       </c>
       <c r="G139" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H139" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I139" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J139">
         <v>-3</v>
       </c>
       <c r="K139" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L139">
         <v>8</v>
       </c>
-      <c r="R139" t="s">
-        <v>30</v>
-      </c>
-      <c r="S139" t="s">
-        <v>72</v>
-      </c>
-      <c r="U139" t="s">
-        <v>30</v>
-      </c>
-      <c r="X139">
+      <c r="P139" t="s">
+        <v>88</v>
+      </c>
+      <c r="W139" t="s">
+        <v>34</v>
+      </c>
+      <c r="X139" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB139">
         <v>9</v>
       </c>
     </row>
@@ -7181,7 +7769,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -7193,33 +7781,36 @@
         <v>7</v>
       </c>
       <c r="G140" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H140" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I140" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J140">
         <v>-10</v>
       </c>
       <c r="K140" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L140">
         <v>8</v>
       </c>
-      <c r="R140" t="s">
-        <v>36</v>
-      </c>
-      <c r="S140" t="s">
-        <v>89</v>
-      </c>
-      <c r="U140" t="s">
-        <v>30</v>
-      </c>
-      <c r="X140">
+      <c r="P140" t="s">
+        <v>88</v>
+      </c>
+      <c r="W140" t="s">
+        <v>42</v>
+      </c>
+      <c r="X140" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB140">
         <v>9</v>
       </c>
     </row>
@@ -7231,7 +7822,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -7243,33 +7834,36 @@
         <v>17</v>
       </c>
       <c r="G141" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H141" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I141" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J141">
         <v>5</v>
       </c>
       <c r="K141" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L141">
         <v>7</v>
       </c>
-      <c r="R141" t="s">
-        <v>36</v>
-      </c>
-      <c r="S141" t="s">
-        <v>66</v>
-      </c>
-      <c r="U141" t="s">
-        <v>30</v>
-      </c>
-      <c r="X141">
+      <c r="P141" t="s">
+        <v>61</v>
+      </c>
+      <c r="W141" t="s">
+        <v>42</v>
+      </c>
+      <c r="X141" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB141">
         <v>9</v>
       </c>
     </row>
@@ -7281,7 +7875,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D142">
         <v>3</v>
@@ -7293,33 +7887,36 @@
         <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H142" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I142" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J142">
         <v>-3</v>
       </c>
       <c r="K142" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L142">
         <v>8</v>
       </c>
-      <c r="R142" t="s">
-        <v>36</v>
-      </c>
-      <c r="S142" t="s">
-        <v>72</v>
-      </c>
-      <c r="U142" t="s">
-        <v>36</v>
-      </c>
-      <c r="X142">
+      <c r="P142" t="s">
+        <v>88</v>
+      </c>
+      <c r="W142" t="s">
+        <v>42</v>
+      </c>
+      <c r="X142" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB142">
         <v>9</v>
       </c>
     </row>
@@ -7331,7 +7928,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D143">
         <v>4</v>
@@ -7343,15 +7940,15 @@
         <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H143" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="I143" t="s">
-        <v>70</v>
-      </c>
-      <c r="X143">
+        <v>86</v>
+      </c>
+      <c r="AB143">
         <v>9</v>
       </c>
     </row>
@@ -7363,7 +7960,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -7375,15 +7972,15 @@
         <v>-40</v>
       </c>
       <c r="G144" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H144" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I144" t="s">
-        <v>28</v>
-      </c>
-      <c r="X144">
+        <v>32</v>
+      </c>
+      <c r="AB144">
         <v>9</v>
       </c>
     </row>
@@ -7395,7 +7992,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -7407,19 +8004,19 @@
         <v>-20</v>
       </c>
       <c r="G145" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H145" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I145" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L145">
         <v>6</v>
@@ -7430,19 +8027,25 @@
       <c r="O145">
         <v>8</v>
       </c>
-      <c r="R145" t="s">
-        <v>30</v>
-      </c>
-      <c r="S145" t="s">
-        <v>62</v>
-      </c>
-      <c r="U145" t="s">
-        <v>36</v>
-      </c>
-      <c r="W145">
+      <c r="P145" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>47</v>
+      </c>
+      <c r="S145">
         <v>6</v>
       </c>
-      <c r="X145">
+      <c r="W145" t="s">
+        <v>34</v>
+      </c>
+      <c r="X145" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB145">
         <v>11</v>
       </c>
     </row>
@@ -7454,7 +8057,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -7466,39 +8069,42 @@
         <v>-20</v>
       </c>
       <c r="G146" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H146" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I146" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J146">
         <v>9</v>
       </c>
       <c r="K146" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L146">
         <v>6</v>
       </c>
       <c r="M146" t="s">
-        <v>29</v>
-      </c>
-      <c r="R146" t="s">
-        <v>36</v>
-      </c>
-      <c r="S146" t="s">
-        <v>72</v>
-      </c>
-      <c r="U146" t="s">
-        <v>30</v>
-      </c>
-      <c r="W146">
+        <v>33</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>47</v>
+      </c>
+      <c r="S146">
         <v>6</v>
       </c>
-      <c r="X146">
+      <c r="W146" t="s">
+        <v>42</v>
+      </c>
+      <c r="X146" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB146">
         <v>11</v>
       </c>
     </row>
@@ -7510,7 +8116,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -7522,39 +8128,42 @@
         <v>-29</v>
       </c>
       <c r="G147" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H147" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I147" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J147">
         <v>-2</v>
       </c>
       <c r="K147" t="s">
+        <v>37</v>
+      </c>
+      <c r="L147">
+        <v>7</v>
+      </c>
+      <c r="M147" t="s">
         <v>33</v>
       </c>
-      <c r="L147">
-        <v>7</v>
-      </c>
-      <c r="M147" t="s">
-        <v>29</v>
-      </c>
-      <c r="R147" t="s">
-        <v>30</v>
-      </c>
-      <c r="S147" t="s">
-        <v>90</v>
-      </c>
-      <c r="U147" t="s">
-        <v>30</v>
-      </c>
-      <c r="W147">
+      <c r="Q147" t="s">
+        <v>47</v>
+      </c>
+      <c r="S147">
         <v>6</v>
       </c>
-      <c r="X147">
+      <c r="W147" t="s">
+        <v>34</v>
+      </c>
+      <c r="X147" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB147">
         <v>11</v>
       </c>
     </row>
@@ -7566,7 +8175,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D148">
         <v>4</v>
@@ -7578,15 +8187,15 @@
         <v>-27</v>
       </c>
       <c r="G148" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H148" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I148" t="s">
-        <v>65</v>
-      </c>
-      <c r="X148">
+        <v>81</v>
+      </c>
+      <c r="AB148">
         <v>11</v>
       </c>
     </row>
@@ -7598,7 +8207,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -7610,36 +8219,39 @@
         <v>-40</v>
       </c>
       <c r="G149" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H149" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I149" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J149">
         <v>6</v>
       </c>
       <c r="K149" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L149">
         <v>7</v>
       </c>
-      <c r="Q149">
+      <c r="P149" t="s">
+        <v>88</v>
+      </c>
+      <c r="V149">
         <v>0</v>
       </c>
-      <c r="R149" t="s">
-        <v>36</v>
-      </c>
-      <c r="S149" t="s">
-        <v>72</v>
-      </c>
-      <c r="U149" t="s">
-        <v>30</v>
-      </c>
-      <c r="X149">
+      <c r="W149" t="s">
+        <v>42</v>
+      </c>
+      <c r="X149" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB149">
         <v>10</v>
       </c>
     </row>
@@ -7651,7 +8263,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -7663,33 +8275,36 @@
         <v>-46</v>
       </c>
       <c r="G150" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H150" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J150">
         <v>4</v>
       </c>
       <c r="K150" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L150">
         <v>7</v>
       </c>
-      <c r="R150" t="s">
-        <v>36</v>
-      </c>
-      <c r="S150" t="s">
-        <v>72</v>
-      </c>
-      <c r="U150" t="s">
-        <v>30</v>
-      </c>
-      <c r="X150">
+      <c r="P150" t="s">
+        <v>88</v>
+      </c>
+      <c r="W150" t="s">
+        <v>42</v>
+      </c>
+      <c r="X150" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB150">
         <v>10</v>
       </c>
     </row>
@@ -7701,7 +8316,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -7713,33 +8328,36 @@
         <v>50</v>
       </c>
       <c r="G151" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H151" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I151" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J151">
         <v>2</v>
       </c>
       <c r="K151" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L151">
         <v>6</v>
       </c>
-      <c r="R151" t="s">
-        <v>36</v>
-      </c>
-      <c r="S151" t="s">
-        <v>72</v>
-      </c>
-      <c r="U151" t="s">
-        <v>36</v>
-      </c>
-      <c r="X151">
+      <c r="P151" t="s">
+        <v>88</v>
+      </c>
+      <c r="W151" t="s">
+        <v>42</v>
+      </c>
+      <c r="X151" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB151">
         <v>10</v>
       </c>
     </row>
